--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040C20AE-C20A-7949-9A51-60B7B7D35D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665611E9-4CE9-C14A-9255-8582750B5400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Datos!$A$1:$AY$82</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3066" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="793">
   <si>
     <t>nombre</t>
   </si>
@@ -2084,9 +2087,6 @@
     <t>Que Rico Restaurante Yanganita</t>
   </si>
   <si>
-    <t>Truchas Corishiro</t>
-  </si>
-  <si>
     <t>Hostería Molino Tropical</t>
   </si>
   <si>
@@ -2409,6 +2409,12 @@
   </si>
   <si>
     <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1766457800/LaCriollita_Vilcabamba_Producto_web__f9iuzl.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1766457794/LaCriollita_Vilcabamba_Infraestructura_web__pokati.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1766457812/LaCriollita_Vilcabamba_Identidad2_web__k1eccg.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1766457817/LaCriollita_Vilcabamba_Infraestructura2_web__ifrffj.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1766457829/LaCriollita_Vilcabamba_Sopa_web__tpmpo9.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1766457823/LaCriollita_Vilcabamba_ProductoCent_web__begsff.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1766457780/LaCriollita_Vilcabamba_Exterior_web__fmvkjb.jpg}</t>
+  </si>
+  <si>
+    <t>Truchas Curishiro</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1770689478/DiosLePague_Chuquiribamba_identidad_Reel__zxtopf.mp4</t>
   </si>
 </sst>
 </file>
@@ -3918,7 +3924,7 @@
         <v>36</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>461</v>
@@ -4067,7 +4073,7 @@
         <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>462</v>
@@ -4218,7 +4224,7 @@
         <v>36</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>463</v>
@@ -4330,12 +4336,14 @@
         <v>38</v>
       </c>
       <c r="AW4" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AX4" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="AY4" s="7"/>
+        <v>742</v>
+      </c>
+      <c r="AY4" s="7" t="s">
+        <v>792</v>
+      </c>
     </row>
     <row r="5" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="3" t="s">
@@ -4369,7 +4377,7 @@
         <v>36</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>488</v>
@@ -4481,10 +4489,10 @@
         <v>38</v>
       </c>
       <c r="AW5" s="6" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AX5" s="9" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AY5" s="7"/>
     </row>
@@ -4520,7 +4528,7 @@
         <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>490</v>
@@ -4545,7 +4553,7 @@
         <v>483</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="U6" s="4">
         <v>5</v>
@@ -4671,7 +4679,7 @@
         <v>36</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>492</v>
@@ -4822,7 +4830,7 @@
         <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>493</v>
@@ -4847,7 +4855,7 @@
         <v>483</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="U8" s="4">
         <v>4</v>
@@ -4973,7 +4981,7 @@
         <v>36</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>494</v>
@@ -5124,7 +5132,7 @@
         <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>493</v>
@@ -5275,7 +5283,7 @@
         <v>36</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>490</v>
@@ -5300,7 +5308,7 @@
         <v>483</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="U11" s="4">
         <v>4</v>
@@ -5387,10 +5395,10 @@
         <v>38</v>
       </c>
       <c r="AW11" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AX11" s="9" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AY11" s="7"/>
     </row>
@@ -5426,7 +5434,7 @@
         <v>36</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>462</v>
@@ -5451,7 +5459,7 @@
         <v>483</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="U12" s="4">
         <v>4</v>
@@ -5602,7 +5610,7 @@
         <v>483</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="U13" s="4">
         <v>3</v>
@@ -5753,7 +5761,7 @@
         <v>483</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="U14" s="4">
         <v>3</v>
@@ -5991,10 +5999,10 @@
         <v>38</v>
       </c>
       <c r="AW15" s="6" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AX15" s="9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AY15" s="7"/>
     </row>
@@ -6210,7 +6218,7 @@
         <v>483</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="U17" s="4">
         <v>5</v>
@@ -6512,7 +6520,7 @@
         <v>483</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="U19" s="4">
         <v>5</v>
@@ -6665,7 +6673,7 @@
         <v>495</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="U20" s="4">
         <v>5</v>
@@ -6816,7 +6824,7 @@
         <v>483</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="U21" s="4">
         <v>5</v>
@@ -6903,10 +6911,10 @@
         <v>38</v>
       </c>
       <c r="AW21" s="6" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AX21" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AY21" s="7"/>
     </row>
@@ -7118,7 +7126,7 @@
         <v>483</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="U23" s="4">
         <v>5</v>
@@ -7356,10 +7364,10 @@
         <v>38</v>
       </c>
       <c r="AW24" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AX24" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AY24" s="7"/>
     </row>
@@ -7420,7 +7428,7 @@
         <v>483</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="U25" s="4">
         <v>3</v>
@@ -7571,7 +7579,7 @@
         <v>483</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="U26" s="4">
         <v>3</v>
@@ -7809,10 +7817,10 @@
         <v>38</v>
       </c>
       <c r="AW27" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AX27" s="9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AY27" s="7"/>
     </row>
@@ -7962,10 +7970,10 @@
         <v>38</v>
       </c>
       <c r="AW28" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AX28" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AY28" s="7"/>
     </row>
@@ -8026,7 +8034,7 @@
         <v>483</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="U29" s="4">
         <v>3</v>
@@ -8177,7 +8185,7 @@
         <v>483</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="U30" s="4">
         <v>3</v>
@@ -8328,7 +8336,7 @@
         <v>483</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="U31" s="4">
         <v>3</v>
@@ -8415,10 +8423,10 @@
         <v>38</v>
       </c>
       <c r="AW31" s="6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AX31" s="9" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AY31" s="7"/>
     </row>
@@ -8566,10 +8574,10 @@
         <v>38</v>
       </c>
       <c r="AW32" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AX32" s="9" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AY32" s="7"/>
     </row>
@@ -8717,10 +8725,10 @@
         <v>38</v>
       </c>
       <c r="AW33" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AX33" s="9" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AY33" s="7"/>
     </row>
@@ -9024,7 +9032,7 @@
     </row>
     <row r="36" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>32</v>
@@ -9322,7 +9330,7 @@
     </row>
     <row r="38" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>32</v>
@@ -9352,7 +9360,7 @@
         <v>36</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>521</v>
@@ -9613,16 +9621,16 @@
         <v>38</v>
       </c>
       <c r="AW39" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AX39" s="9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AY39" s="7"/>
     </row>
     <row r="40" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>32</v>
@@ -9764,16 +9772,16 @@
         <v>38</v>
       </c>
       <c r="AW40" s="6" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AX40" s="9" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AY40" s="7"/>
     </row>
     <row r="41" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>36</v>
@@ -10260,7 +10268,7 @@
         <v>36</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>528</v>
@@ -10381,7 +10389,7 @@
     </row>
     <row r="45" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>32</v>
@@ -10825,10 +10833,10 @@
         <v>38</v>
       </c>
       <c r="AW47" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AX47" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AY47" s="7"/>
     </row>
@@ -11131,16 +11139,16 @@
         <v>38</v>
       </c>
       <c r="AW49" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AX49" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AY49" s="7"/>
     </row>
     <row r="50" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>32</v>
@@ -11291,7 +11299,7 @@
     </row>
     <row r="51" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>32</v>
@@ -11433,10 +11441,10 @@
         <v>38</v>
       </c>
       <c r="AW51" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AX51" s="9" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AY51" s="7"/>
     </row>
@@ -11593,7 +11601,7 @@
     </row>
     <row r="53" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>32</v>
@@ -11735,10 +11743,10 @@
         <v>38</v>
       </c>
       <c r="AW53" s="6" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AX53" s="9" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AY53" s="7"/>
     </row>
@@ -11774,7 +11782,7 @@
         <v>36</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>545</v>
@@ -11895,7 +11903,7 @@
     </row>
     <row r="55" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>32</v>
@@ -12350,7 +12358,7 @@
     </row>
     <row r="58" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>683</v>
+        <v>791</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>32</v>
@@ -12656,7 +12664,7 @@
     </row>
     <row r="60" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>36</v>
@@ -12809,7 +12817,7 @@
     </row>
     <row r="61" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>32</v>
@@ -12962,7 +12970,7 @@
     </row>
     <row r="62" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>32</v>
@@ -12992,7 +13000,7 @@
         <v>36</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>558</v>
@@ -13145,7 +13153,7 @@
         <v>36</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>560</v>
@@ -13259,16 +13267,16 @@
         <v>38</v>
       </c>
       <c r="AW63" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AX63" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AY63" s="7"/>
     </row>
     <row r="64" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>32</v>
@@ -13298,7 +13306,7 @@
         <v>36</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>563</v>
@@ -13449,7 +13457,7 @@
         <v>36</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>566</v>
@@ -13598,7 +13606,7 @@
         <v>36</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>543</v>
@@ -13749,7 +13757,7 @@
         <v>36</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>569</v>
@@ -13861,10 +13869,10 @@
         <v>38</v>
       </c>
       <c r="AW67" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AX67" s="9" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AY67" s="7"/>
     </row>
@@ -13900,7 +13908,7 @@
         <v>36</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>543</v>
@@ -14053,7 +14061,7 @@
         <v>36</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>543</v>
@@ -14204,7 +14212,7 @@
         <v>36</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>543</v>
@@ -14357,7 +14365,7 @@
         <v>36</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>574</v>
@@ -14510,7 +14518,7 @@
         <v>36</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>543</v>
@@ -14661,7 +14669,7 @@
         <v>36</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>543</v>
@@ -14810,7 +14818,7 @@
         <v>36</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>543</v>
@@ -14922,16 +14930,16 @@
         <v>38</v>
       </c>
       <c r="AW74" s="6" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="AX74" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="AY74" s="7"/>
     </row>
     <row r="75" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>32</v>
@@ -14961,7 +14969,7 @@
         <v>36</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>462</v>
@@ -15112,7 +15120,7 @@
         <v>36</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>543</v>
@@ -15226,16 +15234,16 @@
         <v>38</v>
       </c>
       <c r="AW76" s="6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AX76" s="9" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AY76" s="7"/>
     </row>
     <row r="77" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>32</v>
@@ -15265,7 +15273,7 @@
         <v>36</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>462</v>
@@ -15379,10 +15387,10 @@
         <v>38</v>
       </c>
       <c r="AW77" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AX77" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AY77" s="7"/>
     </row>
@@ -15418,7 +15426,7 @@
         <v>36</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>581</v>
@@ -15539,7 +15547,7 @@
     </row>
     <row r="79" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>32</v>
@@ -15569,7 +15577,7 @@
         <v>36</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>543</v>
@@ -15690,7 +15698,7 @@
     </row>
     <row r="80" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>32</v>
@@ -15720,7 +15728,7 @@
         <v>36</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>543</v>
@@ -15843,7 +15851,7 @@
     </row>
     <row r="81" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>32</v>
@@ -15987,16 +15995,16 @@
         <v>38</v>
       </c>
       <c r="AW81" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AX81" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AY81" s="7"/>
     </row>
     <row r="82" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>32</v>
@@ -16026,7 +16034,7 @@
         <v>36</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>543</v>
@@ -16214,6 +16222,7 @@
     <hyperlink ref="AX4" r:id="rId66" xr:uid="{D149E6A5-8ACD-6B4E-A061-227ED71C6C07}"/>
     <hyperlink ref="AX67" r:id="rId67" xr:uid="{813CD1C1-C9D4-F347-B011-D51F37DD49BB}"/>
     <hyperlink ref="AX74" r:id="rId68" xr:uid="{94666C1E-0A40-AD4D-92ED-FEEE0D1225B2}"/>
+    <hyperlink ref="AY4" r:id="rId69" xr:uid="{9001C724-EA1B-D642-A2B1-63102A92F4D9}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665611E9-4CE9-C14A-9255-8582750B5400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191BE004-FCA4-4D4A-BE1B-084E9A370CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3067" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="794">
   <si>
     <t>nombre</t>
   </si>
@@ -2414,7 +2414,10 @@
     <t>Truchas Curishiro</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1770689478/DiosLePague_Chuquiribamba_identidad_Reel__zxtopf.mp4</t>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1770691354/EsconditedeQuezada_Santiago_low_horizontal_tgwsy5.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1770691537/DiosLePague_Chuquiribamba_identidad_low__ozun4i.mp4</t>
   </si>
 </sst>
 </file>
@@ -4341,8 +4344,8 @@
       <c r="AX4" s="9" t="s">
         <v>742</v>
       </c>
-      <c r="AY4" s="7" t="s">
-        <v>792</v>
+      <c r="AY4" s="9" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="5" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14027,7 +14030,9 @@
       <c r="AX68" s="9" t="s">
         <v>631</v>
       </c>
-      <c r="AY68" s="7"/>
+      <c r="AY68" s="9" t="s">
+        <v>792</v>
+      </c>
     </row>
     <row r="69" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
@@ -16222,7 +16227,8 @@
     <hyperlink ref="AX4" r:id="rId66" xr:uid="{D149E6A5-8ACD-6B4E-A061-227ED71C6C07}"/>
     <hyperlink ref="AX67" r:id="rId67" xr:uid="{813CD1C1-C9D4-F347-B011-D51F37DD49BB}"/>
     <hyperlink ref="AX74" r:id="rId68" xr:uid="{94666C1E-0A40-AD4D-92ED-FEEE0D1225B2}"/>
-    <hyperlink ref="AY4" r:id="rId69" xr:uid="{9001C724-EA1B-D642-A2B1-63102A92F4D9}"/>
+    <hyperlink ref="AY68" r:id="rId69" xr:uid="{758E9232-590D-6549-93F0-50F900F6ABB1}"/>
+    <hyperlink ref="AY4" r:id="rId70" xr:uid="{A3FAA7AD-BF8C-2E4B-8FA4-071D12C3D1EA}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191BE004-FCA4-4D4A-BE1B-084E9A370CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B4DC15-2660-C847-AC37-09473CD99A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="840" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3068" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3093" uniqueCount="819">
   <si>
     <t>nombre</t>
   </si>
@@ -2418,6 +2418,81 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1770691537/DiosLePague_Chuquiribamba_identidad_low__ozun4i.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771519591/ChifaYunnan_Malacatos_intro_low_horizontal_hutnsi.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771520232/MamaDigna_Malacatos_intro_low_horizontal_camdu2.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771520376/TropicalFresh_Malacatos_intro_low_horizontal_o79wc5.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771520508/EstanciaAlcivar_Santiago_Full_Horizontal_low_n7havb.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771520703/Killari_Santiago_intro_low_horizontal_f4n1qz.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771520890/PisicolaOrdonez_Santiago_intro_low_horizontal_wfomd4.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771521064/Sariri_Taquil_intro_lowl_horizontal_pf96yv.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771521637/PalmerasdeMachay_Taquil_intro_low_horizontal_u3vskf.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771521816/33ParrillaCafeBar_Vilcabamba_intro_low_horizontal_necy5r.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771521932/Bambu_Vilcabamba_intro_low_horizontal_dsnbvn.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771522132/Dumpings_Noodles_Vilcabamba_intro_low_horizontal_hpzidt.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771522216/Alivinatu_Vilcabamba_intro_low_horizontal_mzdw2b.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771522735/MolinoTropical_Vilcabamba_intro_low_horizontal_hcnmiz.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771522891/IbeliaMommyCoffeeShop_Vilcabamba_intro_low_horizontal_j40cnb.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771523039/LaBaguette_Vilcabamba_intro_low_horizontal_xdppoe.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771523142/LaCreperiadeYannick_Vilcabamba_low_full_horizontal_g4blvb.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771554721/LaTerraza_Vilcabamba_intro_low_horizontal_ssftys.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771554856/MammaSilva_Vilcabamba_intro_low_horizontal_tj4eyg.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771555008/Oriundo_Vilcabamba_intro_low_horizontal_n7yhnn.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771555152/PiedraDura_Vilcabamba_intro_low_horizontal_dwgmie.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771555286/UnitedFalafelOrg_Vilcabamba_intro_low_horizontal_tmtjkt.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771555404/Vilkalitas_Vilcabamba_intro_low_horizontal_wvbj8s.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771555496/VillaBeatriz_Vilcabamba_intro_low_horizontal_x2b4ui.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771555642/MamaEtelvina_Yangana_intro_low_horizontal_zlpsmy.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771555748/TruchasdeCurishiro_Yangana_intro_low_horizontal_inid8c.mp4</t>
   </si>
 </sst>
 </file>
@@ -9031,7 +9106,9 @@
         <v>460</v>
       </c>
       <c r="AX35" s="7"/>
-      <c r="AY35" s="7"/>
+      <c r="AY35" s="9" t="s">
+        <v>796</v>
+      </c>
     </row>
     <row r="36" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
@@ -9478,7 +9555,9 @@
         <v>460</v>
       </c>
       <c r="AX38" s="7"/>
-      <c r="AY38" s="7"/>
+      <c r="AY38" s="9" t="s">
+        <v>795</v>
+      </c>
     </row>
     <row r="39" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
@@ -10084,7 +10163,9 @@
       <c r="AX42" s="9" t="s">
         <v>615</v>
       </c>
-      <c r="AY42" s="7"/>
+      <c r="AY42" s="9" t="s">
+        <v>801</v>
+      </c>
     </row>
     <row r="43" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
@@ -10237,7 +10318,9 @@
       <c r="AX43" s="9" t="s">
         <v>616</v>
       </c>
-      <c r="AY43" s="7"/>
+      <c r="AY43" s="9" t="s">
+        <v>800</v>
+      </c>
     </row>
     <row r="44" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
@@ -10388,7 +10471,9 @@
       <c r="AX44" s="9" t="s">
         <v>617</v>
       </c>
-      <c r="AY44" s="7"/>
+      <c r="AY44" s="9" t="s">
+        <v>811</v>
+      </c>
     </row>
     <row r="45" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
@@ -10539,7 +10624,9 @@
       <c r="AX45" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="AY45" s="7"/>
+      <c r="AY45" s="9" t="s">
+        <v>807</v>
+      </c>
     </row>
     <row r="46" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="3" t="s">
@@ -10841,7 +10928,9 @@
       <c r="AX47" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="AY47" s="7"/>
+      <c r="AY47" s="9" t="s">
+        <v>814</v>
+      </c>
     </row>
     <row r="48" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="3" t="s">
@@ -11147,7 +11236,9 @@
       <c r="AX49" s="9" t="s">
         <v>714</v>
       </c>
-      <c r="AY49" s="7"/>
+      <c r="AY49" s="9" t="s">
+        <v>815</v>
+      </c>
     </row>
     <row r="50" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
@@ -11449,7 +11540,9 @@
       <c r="AX51" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="AY51" s="7"/>
+      <c r="AY51" s="9" t="s">
+        <v>809</v>
+      </c>
     </row>
     <row r="52" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
@@ -11600,7 +11693,9 @@
       <c r="AX52" s="7" t="s">
         <v>621</v>
       </c>
-      <c r="AY52" s="7"/>
+      <c r="AY52" s="9" t="s">
+        <v>804</v>
+      </c>
     </row>
     <row r="53" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
@@ -11751,7 +11846,9 @@
       <c r="AX53" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="AY53" s="7"/>
+      <c r="AY53" s="9" t="s">
+        <v>803</v>
+      </c>
     </row>
     <row r="54" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
@@ -12357,7 +12454,9 @@
       <c r="AX57" s="9" t="s">
         <v>625</v>
       </c>
-      <c r="AY57" s="7"/>
+      <c r="AY57" s="9" t="s">
+        <v>817</v>
+      </c>
     </row>
     <row r="58" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
@@ -12510,7 +12609,9 @@
       <c r="AX58" s="9" t="s">
         <v>626</v>
       </c>
-      <c r="AY58" s="7"/>
+      <c r="AY58" s="9" t="s">
+        <v>818</v>
+      </c>
     </row>
     <row r="59" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="3" t="s">
@@ -12816,7 +12917,9 @@
       <c r="AX60" s="7" t="s">
         <v>628</v>
       </c>
-      <c r="AY60" s="7"/>
+      <c r="AY60" s="9" t="s">
+        <v>806</v>
+      </c>
     </row>
     <row r="61" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
@@ -12969,7 +13072,9 @@
       <c r="AX61" s="7" t="s">
         <v>629</v>
       </c>
-      <c r="AY61" s="7"/>
+      <c r="AY61" s="9" t="s">
+        <v>813</v>
+      </c>
     </row>
     <row r="62" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
@@ -13275,7 +13380,9 @@
       <c r="AX63" s="9" t="s">
         <v>706</v>
       </c>
-      <c r="AY63" s="7"/>
+      <c r="AY63" s="9" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="64" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
@@ -13877,7 +13984,9 @@
       <c r="AX67" s="9" t="s">
         <v>787</v>
       </c>
-      <c r="AY67" s="7"/>
+      <c r="AY67" s="9" t="s">
+        <v>810</v>
+      </c>
     </row>
     <row r="68" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
@@ -14183,7 +14292,9 @@
         <v>460</v>
       </c>
       <c r="AX69" s="7"/>
-      <c r="AY69" s="7"/>
+      <c r="AY69" s="9" t="s">
+        <v>794</v>
+      </c>
     </row>
     <row r="70" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3" t="s">
@@ -14336,7 +14447,9 @@
       <c r="AX70" s="9" t="s">
         <v>632</v>
       </c>
-      <c r="AY70" s="7"/>
+      <c r="AY70" s="9" t="s">
+        <v>816</v>
+      </c>
     </row>
     <row r="71" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3" t="s">
@@ -14489,7 +14602,9 @@
       <c r="AX71" s="9" t="s">
         <v>633</v>
       </c>
-      <c r="AY71" s="7"/>
+      <c r="AY71" s="9" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="72" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3" t="s">
@@ -14640,7 +14755,9 @@
       <c r="AX72" s="9" t="s">
         <v>634</v>
       </c>
-      <c r="AY72" s="7"/>
+      <c r="AY72" s="9" t="s">
+        <v>808</v>
+      </c>
     </row>
     <row r="73" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3" t="s">
@@ -15244,7 +15361,9 @@
       <c r="AX76" s="9" t="s">
         <v>730</v>
       </c>
-      <c r="AY76" s="7"/>
+      <c r="AY76" s="9" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="77" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
@@ -15548,7 +15667,9 @@
       <c r="AX78" s="9" t="s">
         <v>636</v>
       </c>
-      <c r="AY78" s="7"/>
+      <c r="AY78" s="9" t="s">
+        <v>812</v>
+      </c>
     </row>
     <row r="79" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
@@ -15852,7 +15973,9 @@
       <c r="AX80" s="9" t="s">
         <v>585</v>
       </c>
-      <c r="AY80" s="7"/>
+      <c r="AY80" s="9" t="s">
+        <v>798</v>
+      </c>
     </row>
     <row r="81" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
@@ -16154,7 +16277,9 @@
       <c r="AX82" s="7" t="s">
         <v>587</v>
       </c>
-      <c r="AY82" s="7"/>
+      <c r="AY82" s="9" t="s">
+        <v>799</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -16229,6 +16354,31 @@
     <hyperlink ref="AX74" r:id="rId68" xr:uid="{94666C1E-0A40-AD4D-92ED-FEEE0D1225B2}"/>
     <hyperlink ref="AY68" r:id="rId69" xr:uid="{758E9232-590D-6549-93F0-50F900F6ABB1}"/>
     <hyperlink ref="AY4" r:id="rId70" xr:uid="{A3FAA7AD-BF8C-2E4B-8FA4-071D12C3D1EA}"/>
+    <hyperlink ref="AY69" r:id="rId71" xr:uid="{20237335-582F-354C-AFC6-F2C6749713E4}"/>
+    <hyperlink ref="AY38" r:id="rId72" xr:uid="{AC4DA16C-39E7-2E47-954D-E245590A314E}"/>
+    <hyperlink ref="AY35" r:id="rId73" xr:uid="{74D1AA3A-5D36-764E-9D99-906295585AE6}"/>
+    <hyperlink ref="AY71" r:id="rId74" xr:uid="{89DAE256-4128-0145-A255-6924C174EDCC}"/>
+    <hyperlink ref="AY80" r:id="rId75" xr:uid="{0C77A8D2-0A3C-B049-A707-50BFDC557AFF}"/>
+    <hyperlink ref="AY82" r:id="rId76" xr:uid="{3C4B76E8-DC03-5946-B433-B6E6DF9E13DD}"/>
+    <hyperlink ref="AY43" r:id="rId77" xr:uid="{62B9CB02-CB45-5345-BCC0-B7C0743D6392}"/>
+    <hyperlink ref="AY42" r:id="rId78" xr:uid="{FB8530CA-AD1F-3F41-A66B-66746B5A720E}"/>
+    <hyperlink ref="AY76" r:id="rId79" xr:uid="{F9A75549-C163-0B42-99F0-71AB86FF5E06}"/>
+    <hyperlink ref="AY53" r:id="rId80" xr:uid="{A1F2FF69-8941-914C-839B-08031197B516}"/>
+    <hyperlink ref="AY52" r:id="rId81" xr:uid="{7208A52F-430D-A547-98D0-C1DB4F636213}"/>
+    <hyperlink ref="AY63" r:id="rId82" xr:uid="{137EF245-936B-9540-A418-79D16D3EE056}"/>
+    <hyperlink ref="AY60" r:id="rId83" xr:uid="{B07A9345-06E3-7149-AC74-45BF02F75D6A}"/>
+    <hyperlink ref="AY45" r:id="rId84" xr:uid="{0330CE9D-13B2-0E4B-A278-85167FC1074F}"/>
+    <hyperlink ref="AY72" r:id="rId85" xr:uid="{061B6DEF-8033-AC48-BB6F-B07E0F497B13}"/>
+    <hyperlink ref="AY51" r:id="rId86" xr:uid="{7DAFB160-26AA-B44F-912E-6B8BC8A8C67D}"/>
+    <hyperlink ref="AY67" r:id="rId87" xr:uid="{0CFC5F37-67F6-7D41-8A4D-43FF8DBEE6DA}"/>
+    <hyperlink ref="AY44" r:id="rId88" xr:uid="{B70F7B97-F0FC-3046-B424-482B82129980}"/>
+    <hyperlink ref="AY78" r:id="rId89" xr:uid="{0B2889A8-B982-DE43-AC32-97640C3FC4F0}"/>
+    <hyperlink ref="AY61" r:id="rId90" xr:uid="{BB9703CE-2BEA-2E40-AB6E-E764487D5C93}"/>
+    <hyperlink ref="AY47" r:id="rId91" xr:uid="{4A19C8E5-8DC9-2244-9B7A-DFF133598171}"/>
+    <hyperlink ref="AY49" r:id="rId92" xr:uid="{00A98B21-CE4E-F647-8D26-AD313B701E27}"/>
+    <hyperlink ref="AY70" r:id="rId93" xr:uid="{7E02BA1D-6B21-D744-89C9-DFD8DCEF1A5F}"/>
+    <hyperlink ref="AY57" r:id="rId94" xr:uid="{9581E871-6CAC-644D-9095-048B13A794A7}"/>
+    <hyperlink ref="AY58" r:id="rId95" xr:uid="{1EA1FB66-562C-554F-A505-9BFA46852FC8}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B4DC15-2660-C847-AC37-09473CD99A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F29DD2-99DD-E149-B67E-E05E7C605D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="840" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3093" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3099" uniqueCount="831">
   <si>
     <t>nombre</t>
   </si>
@@ -2493,6 +2493,42 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771555748/TruchasdeCurishiro_Yangana_intro_low_horizontal_inid8c.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773152527/ChifaYunnan_Malacatos_fachadaext_web_rblcpc.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773152528/ChifaYunnan_Malacatos_identidad_web_qwto3k.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773152533/ChifaYunnan_Malacatos_productocent_web_grovys.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773152540/ChifaYunnan_Malacatos_productodiag2_web_bol8z6.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773152544/ChifaYunnan_Malacatos_productodig_web_qjpiyr.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773152570/ChifaYunnan_Malacatos_productofront_web_fqc9my.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773152573/ChifaYunnan_Malacatos_productosenital_web_x98ovc.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153033/MamaDigna_Malacatos_identidad_web_dlycnw.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153039/MamaDigna_Malacatos_prodfront_web__o0dm4u.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153044/MamaDigna_Malacatos_producfrnh_web_nl2p1u.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153047/MamaDigna_Malacatos_producfrnt_web_nf1c11.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153056/MamaDigna_Malacatos_productodet__fwnsj7.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153238/TropicalFresh_Malacatos_identidad_web_ierqtq.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153242/TropicalFresh_Malacatos_espacioint_web_cnzq0t.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153248/TropicalFresh_Malacatos_fachadaext_web_lbzany.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153253/TropicalFresh_Malacatos_productofrnt_web_oxeamo.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153261/TropicalFresh_Malacatos_productosent2_web_fygxbn.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153265/TropicalFresh_Malacatos_productosent_web_igcriq.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153473/AsadosDonaBachita_Malacatos_extrest_web__qktwrk.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153478/AsadosDonaBachita_Malacatos_ident_web__y6z6hu.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153491/AsadosDonaBachita_Malacatos_prdrestfront_web__shgcsn.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153484/AsadosDonaBachita_Malacatos_intrest_web__wcgm0s.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153496/AsadosDonaBachita_Malacatos_prdrest_web__jwaopg.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153504/AsadosDonaBachita_Malacatos_proddtls_web__zoortq.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153509/AsadosDonaBachita_Malacatos_proddetlls_web__i6djcv.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153514/AsadosDonaBachita_Malacatos_prodfrontl_web__rflfpz.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153871/BurguerExpress_Vilcabamba_extdig_web__l0all6.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153876/BurguerExpress_Vilcabamba_identfronyt_web__y5gksp.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153882/BurguerExpress_Vilcabamba_intdig_web__ukhscc.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153889/BurguerExpress_Vilcabamba_intfrnt_web__b6dym7.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153898/BurguerExpress_Vilcabamba_product_web__xmrvoy.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773153904/BurguerExpress_Vilcabamba_productcent_web__sb1fir.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154061/PeruMarCarnes_Mariscos_Malacatos_web_1_xlbb7k.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154077/PeruMarCarnes_Mariscos_Malacatos_web_3_vt2xqw.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154084/PeruMarCarnes_Mariscos_Malacatos_web_6_s9mecs.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154092/PeruMarCarnes_Mariscos_Malacatos_web_8_rsgq9o.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154099/PeruMarCarnes_Mariscos_Malacatos_web_7_eeoovz.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154106/PeruMarCarnes_Mariscos_Malacatos_web_9_tzwdv8.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154113/PeruMarCarnes_Mariscos_Malacatos_web_12_rgx3lt.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154121/PeruMarCarnes_Mariscos_Malacatos_web_10_fzdosv.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154128/PeruMarCarnes_Mariscos_Malacatos_web_11_nwpfae.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154135/PeruMarCarnes_Mariscos_Malacatos_web_13_grlljo.jpg}</t>
   </si>
 </sst>
 </file>
@@ -8954,9 +8990,11 @@
         <v>38</v>
       </c>
       <c r="AW34" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX34" s="7"/>
+        <v>828</v>
+      </c>
+      <c r="AX34" s="9" t="s">
+        <v>827</v>
+      </c>
       <c r="AY34" s="7"/>
     </row>
     <row r="35" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9103,9 +9141,11 @@
         <v>38</v>
       </c>
       <c r="AW35" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX35" s="7"/>
+        <v>824</v>
+      </c>
+      <c r="AX35" s="9" t="s">
+        <v>823</v>
+      </c>
       <c r="AY35" s="9" t="s">
         <v>796</v>
       </c>
@@ -9254,9 +9294,11 @@
         <v>38</v>
       </c>
       <c r="AW36" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX36" s="7"/>
+        <v>830</v>
+      </c>
+      <c r="AX36" s="9" t="s">
+        <v>829</v>
+      </c>
       <c r="AY36" s="7"/>
     </row>
     <row r="37" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9403,9 +9445,11 @@
         <v>38</v>
       </c>
       <c r="AW37" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX37" s="7"/>
+        <v>826</v>
+      </c>
+      <c r="AX37" s="9" t="s">
+        <v>825</v>
+      </c>
       <c r="AY37" s="7"/>
     </row>
     <row r="38" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9552,9 +9596,11 @@
         <v>38</v>
       </c>
       <c r="AW38" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX38" s="7"/>
+        <v>822</v>
+      </c>
+      <c r="AX38" s="9" t="s">
+        <v>821</v>
+      </c>
       <c r="AY38" s="9" t="s">
         <v>795</v>
       </c>
@@ -14289,9 +14335,11 @@
         <v>38</v>
       </c>
       <c r="AW69" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX69" s="7"/>
+        <v>820</v>
+      </c>
+      <c r="AX69" s="9" t="s">
+        <v>819</v>
+      </c>
       <c r="AY69" s="9" t="s">
         <v>794</v>
       </c>
@@ -16379,6 +16427,12 @@
     <hyperlink ref="AY70" r:id="rId93" xr:uid="{7E02BA1D-6B21-D744-89C9-DFD8DCEF1A5F}"/>
     <hyperlink ref="AY57" r:id="rId94" xr:uid="{9581E871-6CAC-644D-9095-048B13A794A7}"/>
     <hyperlink ref="AY58" r:id="rId95" xr:uid="{1EA1FB66-562C-554F-A505-9BFA46852FC8}"/>
+    <hyperlink ref="AX69" r:id="rId96" xr:uid="{748732B9-0DE4-7646-A18C-6A1679407E95}"/>
+    <hyperlink ref="AX38" r:id="rId97" xr:uid="{E36BC834-9005-8440-8821-FA488151234C}"/>
+    <hyperlink ref="AX35" r:id="rId98" xr:uid="{177492E4-003B-8147-A453-B13DA77CFD3C}"/>
+    <hyperlink ref="AX37" r:id="rId99" xr:uid="{DFCFD8C7-6C85-9347-A4BC-7F1D71C57408}"/>
+    <hyperlink ref="AX34" r:id="rId100" xr:uid="{4BB8D40B-2169-6A4A-99D2-79805F513C89}"/>
+    <hyperlink ref="AX36" r:id="rId101" xr:uid="{38D9667A-6B3B-5E47-A983-C1EC690553CB}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35F29DD2-99DD-E149-B67E-E05E7C605D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80013B5-24DB-984E-A36A-2C4B9C8477A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3099" uniqueCount="831">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3101" uniqueCount="835">
   <si>
     <t>nombre</t>
   </si>
@@ -2021,9 +2021,6 @@
     <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193482/SabordelCampo_Taquil_idnt_web__fbrhsz.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193465/SabordelCampo_Taquil_prodtlio_web__kv60i8.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193500/SabordelCampo_Taquil_prddetalle_web__an3x8j.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193518/SabordelCampo_Taquil_prod_web__spbtxm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193538/SabordelCampo_Taquil_prodpg_web__zfrezm.jpg}</t>
   </si>
   <si>
-    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193122/Machay_Taquil_ident_web__j6dcav.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193105/Machay_Taquil_proddetll_web__ge6i6e.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193139/Machay_Taquil_int_web__bc8edc.jpg,_https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193156/Machay_Taquil_prodcentm_web__hm0q1f.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193172/Machay_Taquil_prodcompl_web__p4058g.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193190/Machay_Taquil_proddetllp2_web__g7oiyh.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193207/Machay_Taquil_prodpcent_web__rziu4y.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193226/Machay_Taquil_prodredm_web__xquvlx.jpg}</t>
-  </si>
-  <si>
     <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193757/Sariri_Taquil_prodcent_web__hwvcxr.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193793/Sariri_Taquil_prodant_web__jp1ggm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193812/Sariri_Taquil_prodbbdey_web__l9ne3z.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193830/Sariri_Taquil_proddetal_web__khcpsz.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193848/Sariri_Taquil_prodjusber_web__tjmpk2.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193866/Sariri_Taquil_prodmdpd_web__v6vh9r.jpg}</t>
   </si>
   <si>
@@ -2231,9 +2228,6 @@
     <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443138/Parrilla_CafeBar_Vilcabamba_02_ea6aej.jpg</t>
   </si>
   <si>
-    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443153/Parrilla_CafeBar_Vilcabamba_Fachadalaterak_web__iwtbeq.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443163/Parrilla_CafeBar_Vilcabamba_04_w4t4di.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443172/Parrilla_CafeBar_Vilcabamba_06_cavo8q.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443182/Parrilla_CafeBar_Vilcabamba_Instalaciones_web__fzk92k.jpg}</t>
-  </si>
-  <si>
     <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443479/MamaFlora_Gualel_fachadad_web__t4fkq1.jpg</t>
   </si>
   <si>
@@ -2529,6 +2523,24 @@
   </si>
   <si>
     <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154077/PeruMarCarnes_Mariscos_Malacatos_web_3_vt2xqw.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154084/PeruMarCarnes_Mariscos_Malacatos_web_6_s9mecs.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154092/PeruMarCarnes_Mariscos_Malacatos_web_8_rsgq9o.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154099/PeruMarCarnes_Mariscos_Malacatos_web_7_eeoovz.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154106/PeruMarCarnes_Mariscos_Malacatos_web_9_tzwdv8.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154113/PeruMarCarnes_Mariscos_Malacatos_web_12_rgx3lt.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154121/PeruMarCarnes_Mariscos_Malacatos_web_10_fzdosv.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154128/PeruMarCarnes_Mariscos_Malacatos_web_11_nwpfae.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154135/PeruMarCarnes_Mariscos_Malacatos_web_13_grlljo.jpg}</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157828/33ParrillaCafeBar_Vilcabamba_identidad_web_jwhecv.jpg,https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157835/33ParrillaCafeBar_Vilcabamba_productodtsen_web_n2v5vj.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157843/33ParrillaCafeBar_Vilcabamba_productofrnt_web_zcy6bm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157851/33ParrillaCafeBar_Vilcabamba_productodett_web_bqu2hd.jpg https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443153/Parrilla_CafeBar_Vilcabamba_Fachadalaterak_web__iwtbeq.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443163/Parrilla_CafeBar_Vilcabamba_04_w4t4di.jpg}</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193122/Machay_Taquil_ident_web__j6dcav.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193105/Machay_Taquil_proddetll_web__ge6i6e.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193139/Machay_Taquil_int_web__bc8edc.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193156/Machay_Taquil_prodcentm_web__hm0q1f.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193172/Machay_Taquil_prodcompl_web__p4058g.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193190/Machay_Taquil_proddetllp2_web__g7oiyh.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193207/Machay_Taquil_prodpcent_web__rziu4y.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193226/Machay_Taquil_prodredm_web__xquvlx.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773158409/Gabriela_Malacatos_fachadaext_web_zndr0g.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773158397/Gabriela_Malacatos_espacioint_web_s7vfns.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773158417/Gabriela_Malacatos_indenthozt_web_fgavwv.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773158426/Gabriela_Malacatos_productofront_web_a4ehsm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773158435/Gabriela_Malacatos_productosent_web_gtywmb.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159354/GerryPizzeria_Malacatos_idnt_web_hvh4tk.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159365/GerryPizzeria_Malacatos_productofrntdt_web_h1eq7s.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159375/GerryPizzeria_Malacatos_productofrnt_web_nwkkqj.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159384/GerryPizzeria_Malacatos_productsentdet_web_fnnorm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159392/GerryPizzeria_Malacatos_productsentdetl_web_yb5yx4.jpg}</t>
   </si>
 </sst>
 </file>
@@ -4038,7 +4050,7 @@
         <v>36</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>461</v>
@@ -4187,7 +4199,7 @@
         <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>462</v>
@@ -4338,7 +4350,7 @@
         <v>36</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>463</v>
@@ -4450,13 +4462,13 @@
         <v>38</v>
       </c>
       <c r="AW4" s="6" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="AX4" s="9" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="AY4" s="9" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="5" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4491,7 +4503,7 @@
         <v>36</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>488</v>
@@ -4603,10 +4615,10 @@
         <v>38</v>
       </c>
       <c r="AW5" s="6" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="AX5" s="9" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="AY5" s="7"/>
     </row>
@@ -4642,7 +4654,7 @@
         <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>490</v>
@@ -4667,7 +4679,7 @@
         <v>483</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="U6" s="4">
         <v>5</v>
@@ -4793,7 +4805,7 @@
         <v>36</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>492</v>
@@ -4944,7 +4956,7 @@
         <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>493</v>
@@ -4969,7 +4981,7 @@
         <v>483</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="U8" s="4">
         <v>4</v>
@@ -5095,7 +5107,7 @@
         <v>36</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>494</v>
@@ -5246,7 +5258,7 @@
         <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>493</v>
@@ -5397,7 +5409,7 @@
         <v>36</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>490</v>
@@ -5422,7 +5434,7 @@
         <v>483</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="U11" s="4">
         <v>4</v>
@@ -5509,10 +5521,10 @@
         <v>38</v>
       </c>
       <c r="AW11" s="6" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AX11" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AY11" s="7"/>
     </row>
@@ -5548,7 +5560,7 @@
         <v>36</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>462</v>
@@ -5573,7 +5585,7 @@
         <v>483</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="U12" s="4">
         <v>4</v>
@@ -5724,7 +5736,7 @@
         <v>483</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="U13" s="4">
         <v>3</v>
@@ -5875,7 +5887,7 @@
         <v>483</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="U14" s="4">
         <v>3</v>
@@ -6113,10 +6125,10 @@
         <v>38</v>
       </c>
       <c r="AW15" s="6" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AX15" s="9" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AY15" s="7"/>
     </row>
@@ -6332,7 +6344,7 @@
         <v>483</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="U17" s="4">
         <v>5</v>
@@ -6634,7 +6646,7 @@
         <v>483</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="U19" s="4">
         <v>5</v>
@@ -6787,7 +6799,7 @@
         <v>495</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="U20" s="4">
         <v>5</v>
@@ -6938,7 +6950,7 @@
         <v>483</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="U21" s="4">
         <v>5</v>
@@ -7025,10 +7037,10 @@
         <v>38</v>
       </c>
       <c r="AW21" s="6" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AX21" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AY21" s="7"/>
     </row>
@@ -7240,7 +7252,7 @@
         <v>483</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="U23" s="4">
         <v>5</v>
@@ -7478,10 +7490,10 @@
         <v>38</v>
       </c>
       <c r="AW24" s="6" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AX24" s="9" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AY24" s="7"/>
     </row>
@@ -7542,7 +7554,7 @@
         <v>483</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="U25" s="4">
         <v>3</v>
@@ -7693,7 +7705,7 @@
         <v>483</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="U26" s="4">
         <v>3</v>
@@ -7931,10 +7943,10 @@
         <v>38</v>
       </c>
       <c r="AW27" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AX27" s="9" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AY27" s="7"/>
     </row>
@@ -8084,10 +8096,10 @@
         <v>38</v>
       </c>
       <c r="AW28" s="6" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AX28" s="9" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AY28" s="7"/>
     </row>
@@ -8148,7 +8160,7 @@
         <v>483</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="U29" s="4">
         <v>3</v>
@@ -8299,7 +8311,7 @@
         <v>483</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="U30" s="4">
         <v>3</v>
@@ -8450,7 +8462,7 @@
         <v>483</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="U31" s="4">
         <v>3</v>
@@ -8537,10 +8549,10 @@
         <v>38</v>
       </c>
       <c r="AW31" s="6" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="AX31" s="9" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="AY31" s="7"/>
     </row>
@@ -8688,10 +8700,10 @@
         <v>38</v>
       </c>
       <c r="AW32" s="6" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="AX32" s="9" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="AY32" s="7"/>
     </row>
@@ -8839,10 +8851,10 @@
         <v>38</v>
       </c>
       <c r="AW33" s="6" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="AX33" s="9" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="AY33" s="7"/>
     </row>
@@ -8990,10 +9002,10 @@
         <v>38</v>
       </c>
       <c r="AW34" s="6" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="AX34" s="9" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="AY34" s="7"/>
     </row>
@@ -9141,18 +9153,18 @@
         <v>38</v>
       </c>
       <c r="AW35" s="6" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="AX35" s="9" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AY35" s="9" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="36" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>32</v>
@@ -9294,10 +9306,10 @@
         <v>38</v>
       </c>
       <c r="AW36" s="6" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="AX36" s="9" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="AY36" s="7"/>
     </row>
@@ -9445,16 +9457,16 @@
         <v>38</v>
       </c>
       <c r="AW37" s="6" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="AX37" s="9" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="AY37" s="7"/>
     </row>
     <row r="38" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>32</v>
@@ -9484,7 +9496,7 @@
         <v>36</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="L38" s="3" t="s">
         <v>521</v>
@@ -9596,13 +9608,13 @@
         <v>38</v>
       </c>
       <c r="AW38" s="6" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="AX38" s="9" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="AY38" s="9" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="39" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9749,16 +9761,16 @@
         <v>38</v>
       </c>
       <c r="AW39" s="6" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AX39" s="9" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AY39" s="7"/>
     </row>
     <row r="40" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>32</v>
@@ -9900,16 +9912,16 @@
         <v>38</v>
       </c>
       <c r="AW40" s="6" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="AX40" s="9" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="AY40" s="7"/>
     </row>
     <row r="41" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>36</v>
@@ -10204,13 +10216,13 @@
         <v>38</v>
       </c>
       <c r="AW42" s="6" t="s">
-        <v>661</v>
+        <v>830</v>
       </c>
       <c r="AX42" s="9" t="s">
         <v>615</v>
       </c>
       <c r="AY42" s="9" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="43" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10359,18 +10371,18 @@
         <v>38</v>
       </c>
       <c r="AW43" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AX43" s="9" t="s">
         <v>616</v>
       </c>
       <c r="AY43" s="9" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="44" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>32</v>
@@ -10400,7 +10412,7 @@
         <v>36</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>528</v>
@@ -10512,18 +10524,18 @@
         <v>38</v>
       </c>
       <c r="AW44" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AX44" s="9" t="s">
         <v>617</v>
       </c>
       <c r="AY44" s="9" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="45" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>32</v>
@@ -10665,13 +10677,13 @@
         <v>38</v>
       </c>
       <c r="AW45" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AX45" s="7" t="s">
         <v>618</v>
       </c>
       <c r="AY45" s="9" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="46" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10969,13 +10981,13 @@
         <v>38</v>
       </c>
       <c r="AW47" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AX47" s="9" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AY47" s="9" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="48" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
@@ -11124,7 +11136,7 @@
         <v>38</v>
       </c>
       <c r="AW48" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AX48" s="9" t="s">
         <v>619</v>
@@ -11277,18 +11289,18 @@
         <v>38</v>
       </c>
       <c r="AW49" s="6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AX49" s="9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AY49" s="9" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="50" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>32</v>
@@ -11430,7 +11442,7 @@
         <v>38</v>
       </c>
       <c r="AW50" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AX50" s="9" t="s">
         <v>620</v>
@@ -11439,7 +11451,7 @@
     </row>
     <row r="51" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>32</v>
@@ -11581,13 +11593,13 @@
         <v>38</v>
       </c>
       <c r="AW51" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AX51" s="9" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AY51" s="9" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="52" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11734,18 +11746,18 @@
         <v>38</v>
       </c>
       <c r="AW52" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AX52" s="7" t="s">
         <v>621</v>
       </c>
       <c r="AY52" s="9" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="53" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>32</v>
@@ -11887,18 +11899,18 @@
         <v>38</v>
       </c>
       <c r="AW53" s="6" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AX53" s="9" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AY53" s="9" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="54" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>32</v>
@@ -11928,7 +11940,7 @@
         <v>36</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="L54" s="3" t="s">
         <v>545</v>
@@ -12040,7 +12052,7 @@
         <v>38</v>
       </c>
       <c r="AW54" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AX54" s="9" t="s">
         <v>622</v>
@@ -12049,7 +12061,7 @@
     </row>
     <row r="55" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>32</v>
@@ -12191,7 +12203,7 @@
         <v>38</v>
       </c>
       <c r="AW55" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AX55" s="9" t="s">
         <v>623</v>
@@ -12342,7 +12354,7 @@
         <v>38</v>
       </c>
       <c r="AW56" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AX56" s="9" t="s">
         <v>624</v>
@@ -12501,12 +12513,12 @@
         <v>625</v>
       </c>
       <c r="AY57" s="9" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="58" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>32</v>
@@ -12656,7 +12668,7 @@
         <v>626</v>
       </c>
       <c r="AY58" s="9" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="59" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12805,7 +12817,7 @@
         <v>38</v>
       </c>
       <c r="AW59" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AX59" s="9" t="s">
         <v>627</v>
@@ -12814,7 +12826,7 @@
     </row>
     <row r="60" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>36</v>
@@ -12958,18 +12970,18 @@
         <v>38</v>
       </c>
       <c r="AW60" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AX60" s="7" t="s">
         <v>628</v>
       </c>
       <c r="AY60" s="9" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="61" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>32</v>
@@ -13113,18 +13125,18 @@
         <v>38</v>
       </c>
       <c r="AW61" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AX61" s="7" t="s">
         <v>629</v>
       </c>
       <c r="AY61" s="9" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="62" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>32</v>
@@ -13154,7 +13166,7 @@
         <v>36</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>558</v>
@@ -13307,7 +13319,7 @@
         <v>36</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>560</v>
@@ -13421,18 +13433,18 @@
         <v>38</v>
       </c>
       <c r="AW63" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AX63" s="9" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AY63" s="9" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="64" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>32</v>
@@ -13462,7 +13474,7 @@
         <v>36</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>563</v>
@@ -13576,9 +13588,11 @@
         <v>38</v>
       </c>
       <c r="AW64" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX64" s="7"/>
+        <v>832</v>
+      </c>
+      <c r="AX64" s="9" t="s">
+        <v>831</v>
+      </c>
       <c r="AY64" s="7"/>
     </row>
     <row r="65" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13613,7 +13627,7 @@
         <v>36</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>566</v>
@@ -13725,9 +13739,11 @@
         <v>38</v>
       </c>
       <c r="AW65" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX65" s="7"/>
+        <v>834</v>
+      </c>
+      <c r="AX65" s="9" t="s">
+        <v>833</v>
+      </c>
       <c r="AY65" s="7"/>
     </row>
     <row r="66" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13762,7 +13778,7 @@
         <v>36</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>543</v>
@@ -13874,7 +13890,7 @@
         <v>38</v>
       </c>
       <c r="AW66" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AX66" s="9" t="s">
         <v>630</v>
@@ -13913,7 +13929,7 @@
         <v>36</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>569</v>
@@ -14025,13 +14041,13 @@
         <v>38</v>
       </c>
       <c r="AW67" s="6" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AX67" s="9" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="AY67" s="9" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="68" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14066,7 +14082,7 @@
         <v>36</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>543</v>
@@ -14180,13 +14196,13 @@
         <v>38</v>
       </c>
       <c r="AW68" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AX68" s="9" t="s">
         <v>631</v>
       </c>
       <c r="AY68" s="9" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="69" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14221,7 +14237,7 @@
         <v>36</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>543</v>
@@ -14335,13 +14351,13 @@
         <v>38</v>
       </c>
       <c r="AW69" s="6" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="AX69" s="9" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="AY69" s="9" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="70" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14376,7 +14392,7 @@
         <v>36</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>543</v>
@@ -14490,13 +14506,13 @@
         <v>38</v>
       </c>
       <c r="AW70" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AX70" s="9" t="s">
         <v>632</v>
       </c>
       <c r="AY70" s="9" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="71" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14531,7 +14547,7 @@
         <v>36</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>574</v>
@@ -14645,13 +14661,13 @@
         <v>38</v>
       </c>
       <c r="AW71" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AX71" s="9" t="s">
         <v>633</v>
       </c>
       <c r="AY71" s="9" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="72" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14686,7 +14702,7 @@
         <v>36</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="L72" s="3" t="s">
         <v>543</v>
@@ -14798,13 +14814,13 @@
         <v>38</v>
       </c>
       <c r="AW72" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AX72" s="9" t="s">
         <v>634</v>
       </c>
       <c r="AY72" s="9" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="73" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14839,7 +14855,7 @@
         <v>36</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="L73" s="3" t="s">
         <v>543</v>
@@ -14988,7 +15004,7 @@
         <v>36</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L74" s="3" t="s">
         <v>543</v>
@@ -15100,16 +15116,16 @@
         <v>38</v>
       </c>
       <c r="AW74" s="6" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="AX74" s="9" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="AY74" s="7"/>
     </row>
     <row r="75" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>32</v>
@@ -15139,7 +15155,7 @@
         <v>36</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="L75" s="3" t="s">
         <v>462</v>
@@ -15251,7 +15267,7 @@
         <v>38</v>
       </c>
       <c r="AW75" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AX75" s="9" t="s">
         <v>635</v>
@@ -15290,7 +15306,7 @@
         <v>36</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="L76" s="3" t="s">
         <v>543</v>
@@ -15404,18 +15420,18 @@
         <v>38</v>
       </c>
       <c r="AW76" s="6" t="s">
-        <v>731</v>
+        <v>829</v>
       </c>
       <c r="AX76" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AY76" s="9" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="77" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>32</v>
@@ -15445,7 +15461,7 @@
         <v>36</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="L77" s="3" t="s">
         <v>462</v>
@@ -15559,10 +15575,10 @@
         <v>38</v>
       </c>
       <c r="AW77" s="6" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AX77" s="9" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AY77" s="7"/>
     </row>
@@ -15598,7 +15614,7 @@
         <v>36</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="L78" s="3" t="s">
         <v>581</v>
@@ -15710,18 +15726,18 @@
         <v>38</v>
       </c>
       <c r="AW78" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="AX78" s="9" t="s">
         <v>636</v>
       </c>
       <c r="AY78" s="9" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="79" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>32</v>
@@ -15751,7 +15767,7 @@
         <v>36</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="L79" s="3" t="s">
         <v>543</v>
@@ -15872,7 +15888,7 @@
     </row>
     <row r="80" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>32</v>
@@ -15902,7 +15918,7 @@
         <v>36</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L80" s="3" t="s">
         <v>543</v>
@@ -16022,12 +16038,12 @@
         <v>585</v>
       </c>
       <c r="AY80" s="9" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="81" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>32</v>
@@ -16171,16 +16187,16 @@
         <v>38</v>
       </c>
       <c r="AW81" s="6" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AX81" s="9" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AY81" s="7"/>
     </row>
     <row r="82" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>32</v>
@@ -16210,7 +16226,7 @@
         <v>36</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="L82" s="3" t="s">
         <v>543</v>
@@ -16326,7 +16342,7 @@
         <v>587</v>
       </c>
       <c r="AY82" s="9" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
   </sheetData>
@@ -16433,6 +16449,8 @@
     <hyperlink ref="AX37" r:id="rId99" xr:uid="{DFCFD8C7-6C85-9347-A4BC-7F1D71C57408}"/>
     <hyperlink ref="AX34" r:id="rId100" xr:uid="{4BB8D40B-2169-6A4A-99D2-79805F513C89}"/>
     <hyperlink ref="AX36" r:id="rId101" xr:uid="{38D9667A-6B3B-5E47-A983-C1EC690553CB}"/>
+    <hyperlink ref="AX64" r:id="rId102" xr:uid="{22E910B8-805C-4742-9546-B50E37BB4BCA}"/>
+    <hyperlink ref="AX65" r:id="rId103" xr:uid="{DB15978D-EAE0-C646-9CB6-EF9193C86E5C}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80013B5-24DB-984E-A36A-2C4B9C8477A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E6DAB1-183A-BE44-AFE8-7863C34A4EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2420,9 +2420,6 @@
     <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771520232/MamaDigna_Malacatos_intro_low_horizontal_camdu2.mp4</t>
   </si>
   <si>
-    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771520376/TropicalFresh_Malacatos_intro_low_horizontal_o79wc5.mp4</t>
-  </si>
-  <si>
     <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1771520508/EstanciaAlcivar_Santiago_Full_Horizontal_low_n7havb.mp4</t>
   </si>
   <si>
@@ -2525,9 +2522,6 @@
     <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154077/PeruMarCarnes_Mariscos_Malacatos_web_3_vt2xqw.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154084/PeruMarCarnes_Mariscos_Malacatos_web_6_s9mecs.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154092/PeruMarCarnes_Mariscos_Malacatos_web_8_rsgq9o.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154099/PeruMarCarnes_Mariscos_Malacatos_web_7_eeoovz.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154106/PeruMarCarnes_Mariscos_Malacatos_web_9_tzwdv8.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154113/PeruMarCarnes_Mariscos_Malacatos_web_12_rgx3lt.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154121/PeruMarCarnes_Mariscos_Malacatos_web_10_fzdosv.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154128/PeruMarCarnes_Mariscos_Malacatos_web_11_nwpfae.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773154135/PeruMarCarnes_Mariscos_Malacatos_web_13_grlljo.jpg}</t>
   </si>
   <si>
-    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157828/33ParrillaCafeBar_Vilcabamba_identidad_web_jwhecv.jpg,https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157835/33ParrillaCafeBar_Vilcabamba_productodtsen_web_n2v5vj.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157843/33ParrillaCafeBar_Vilcabamba_productofrnt_web_zcy6bm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157851/33ParrillaCafeBar_Vilcabamba_productodett_web_bqu2hd.jpg https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443153/Parrilla_CafeBar_Vilcabamba_Fachadalaterak_web__iwtbeq.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443163/Parrilla_CafeBar_Vilcabamba_04_w4t4di.jpg}</t>
-  </si>
-  <si>
     <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193122/Machay_Taquil_ident_web__j6dcav.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193105/Machay_Taquil_proddetll_web__ge6i6e.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193139/Machay_Taquil_int_web__bc8edc.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193156/Machay_Taquil_prodcentm_web__hm0q1f.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193172/Machay_Taquil_prodcompl_web__p4058g.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193190/Machay_Taquil_proddetllp2_web__g7oiyh.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193207/Machay_Taquil_prodpcent_web__rziu4y.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1767193226/Machay_Taquil_prodredm_web__xquvlx.jpg}</t>
   </si>
   <si>
@@ -2541,6 +2535,12 @@
   </si>
   <si>
     <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159365/GerryPizzeria_Malacatos_productofrntdt_web_h1eq7s.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159375/GerryPizzeria_Malacatos_productofrnt_web_nwkkqj.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159384/GerryPizzeria_Malacatos_productsentdet_web_fnnorm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773159392/GerryPizzeria_Malacatos_productsentdetl_web_yb5yx4.jpg}</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157828/33ParrillaCafeBar_Vilcabamba_identidad_web_jwhecv.jpg,https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157835/33ParrillaCafeBar_Vilcabamba_productodtsen_web_n2v5vj.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157843/33ParrillaCafeBar_Vilcabamba_productofrnt_web_zcy6bm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773157851/33ParrillaCafeBar_Vilcabamba_productodett_web_bqu2hd.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443153/Parrilla_CafeBar_Vilcabamba_Fachadalaterak_web__iwtbeq.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768443163/Parrilla_CafeBar_Vilcabamba_04_w4t4di.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1773161315/TropicalFresh_Malacatos_intro_low_horizontall_iodt1i.mp4</t>
   </si>
 </sst>
 </file>
@@ -9002,10 +9002,10 @@
         <v>38</v>
       </c>
       <c r="AW34" s="6" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AX34" s="9" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AY34" s="7"/>
     </row>
@@ -9153,13 +9153,13 @@
         <v>38</v>
       </c>
       <c r="AW35" s="6" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AX35" s="9" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AY35" s="9" t="s">
-        <v>794</v>
+        <v>834</v>
       </c>
     </row>
     <row r="36" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9306,10 +9306,10 @@
         <v>38</v>
       </c>
       <c r="AW36" s="6" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AX36" s="9" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AY36" s="7"/>
     </row>
@@ -9457,10 +9457,10 @@
         <v>38</v>
       </c>
       <c r="AW37" s="6" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AX37" s="9" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AY37" s="7"/>
     </row>
@@ -9608,10 +9608,10 @@
         <v>38</v>
       </c>
       <c r="AW38" s="6" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AX38" s="9" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AY38" s="9" t="s">
         <v>793</v>
@@ -10216,13 +10216,13 @@
         <v>38</v>
       </c>
       <c r="AW42" s="6" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="AX42" s="9" t="s">
         <v>615</v>
       </c>
       <c r="AY42" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="43" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10377,7 +10377,7 @@
         <v>616</v>
       </c>
       <c r="AY43" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="44" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10530,7 +10530,7 @@
         <v>617</v>
       </c>
       <c r="AY44" s="9" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="45" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
@@ -10683,7 +10683,7 @@
         <v>618</v>
       </c>
       <c r="AY45" s="9" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="46" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10987,7 +10987,7 @@
         <v>711</v>
       </c>
       <c r="AY47" s="9" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="48" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
@@ -11295,7 +11295,7 @@
         <v>713</v>
       </c>
       <c r="AY49" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="50" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11599,7 +11599,7 @@
         <v>709</v>
       </c>
       <c r="AY51" s="9" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="52" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11752,7 +11752,7 @@
         <v>621</v>
       </c>
       <c r="AY52" s="9" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="53" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
@@ -11905,7 +11905,7 @@
         <v>727</v>
       </c>
       <c r="AY53" s="9" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="54" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12513,7 +12513,7 @@
         <v>625</v>
       </c>
       <c r="AY57" s="9" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="58" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12668,7 +12668,7 @@
         <v>626</v>
       </c>
       <c r="AY58" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="59" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12976,7 +12976,7 @@
         <v>628</v>
       </c>
       <c r="AY60" s="9" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="61" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13131,7 +13131,7 @@
         <v>629</v>
       </c>
       <c r="AY61" s="9" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="62" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13439,7 +13439,7 @@
         <v>705</v>
       </c>
       <c r="AY63" s="9" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="64" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13588,10 +13588,10 @@
         <v>38</v>
       </c>
       <c r="AW64" s="6" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="AX64" s="9" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="AY64" s="7"/>
     </row>
@@ -13739,10 +13739,10 @@
         <v>38</v>
       </c>
       <c r="AW65" s="6" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AX65" s="9" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="AY65" s="7"/>
     </row>
@@ -14047,7 +14047,7 @@
         <v>785</v>
       </c>
       <c r="AY67" s="9" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="68" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14351,10 +14351,10 @@
         <v>38</v>
       </c>
       <c r="AW69" s="6" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AX69" s="9" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="AY69" s="9" t="s">
         <v>792</v>
@@ -14512,7 +14512,7 @@
         <v>632</v>
       </c>
       <c r="AY70" s="9" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="71" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14667,7 +14667,7 @@
         <v>633</v>
       </c>
       <c r="AY71" s="9" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="72" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14820,7 +14820,7 @@
         <v>634</v>
       </c>
       <c r="AY72" s="9" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="73" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15420,13 +15420,13 @@
         <v>38</v>
       </c>
       <c r="AW76" s="6" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="AX76" s="9" t="s">
         <v>729</v>
       </c>
       <c r="AY76" s="9" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="77" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -15732,7 +15732,7 @@
         <v>636</v>
       </c>
       <c r="AY78" s="9" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="79" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16038,7 +16038,7 @@
         <v>585</v>
       </c>
       <c r="AY80" s="9" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="81" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16342,7 +16342,7 @@
         <v>587</v>
       </c>
       <c r="AY82" s="9" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
   </sheetData>
@@ -16420,37 +16420,37 @@
     <hyperlink ref="AY4" r:id="rId70" xr:uid="{A3FAA7AD-BF8C-2E4B-8FA4-071D12C3D1EA}"/>
     <hyperlink ref="AY69" r:id="rId71" xr:uid="{20237335-582F-354C-AFC6-F2C6749713E4}"/>
     <hyperlink ref="AY38" r:id="rId72" xr:uid="{AC4DA16C-39E7-2E47-954D-E245590A314E}"/>
-    <hyperlink ref="AY35" r:id="rId73" xr:uid="{74D1AA3A-5D36-764E-9D99-906295585AE6}"/>
-    <hyperlink ref="AY71" r:id="rId74" xr:uid="{89DAE256-4128-0145-A255-6924C174EDCC}"/>
-    <hyperlink ref="AY80" r:id="rId75" xr:uid="{0C77A8D2-0A3C-B049-A707-50BFDC557AFF}"/>
-    <hyperlink ref="AY82" r:id="rId76" xr:uid="{3C4B76E8-DC03-5946-B433-B6E6DF9E13DD}"/>
-    <hyperlink ref="AY43" r:id="rId77" xr:uid="{62B9CB02-CB45-5345-BCC0-B7C0743D6392}"/>
-    <hyperlink ref="AY42" r:id="rId78" xr:uid="{FB8530CA-AD1F-3F41-A66B-66746B5A720E}"/>
-    <hyperlink ref="AY76" r:id="rId79" xr:uid="{F9A75549-C163-0B42-99F0-71AB86FF5E06}"/>
-    <hyperlink ref="AY53" r:id="rId80" xr:uid="{A1F2FF69-8941-914C-839B-08031197B516}"/>
-    <hyperlink ref="AY52" r:id="rId81" xr:uid="{7208A52F-430D-A547-98D0-C1DB4F636213}"/>
-    <hyperlink ref="AY63" r:id="rId82" xr:uid="{137EF245-936B-9540-A418-79D16D3EE056}"/>
-    <hyperlink ref="AY60" r:id="rId83" xr:uid="{B07A9345-06E3-7149-AC74-45BF02F75D6A}"/>
-    <hyperlink ref="AY45" r:id="rId84" xr:uid="{0330CE9D-13B2-0E4B-A278-85167FC1074F}"/>
-    <hyperlink ref="AY72" r:id="rId85" xr:uid="{061B6DEF-8033-AC48-BB6F-B07E0F497B13}"/>
-    <hyperlink ref="AY51" r:id="rId86" xr:uid="{7DAFB160-26AA-B44F-912E-6B8BC8A8C67D}"/>
-    <hyperlink ref="AY67" r:id="rId87" xr:uid="{0CFC5F37-67F6-7D41-8A4D-43FF8DBEE6DA}"/>
-    <hyperlink ref="AY44" r:id="rId88" xr:uid="{B70F7B97-F0FC-3046-B424-482B82129980}"/>
-    <hyperlink ref="AY78" r:id="rId89" xr:uid="{0B2889A8-B982-DE43-AC32-97640C3FC4F0}"/>
-    <hyperlink ref="AY61" r:id="rId90" xr:uid="{BB9703CE-2BEA-2E40-AB6E-E764487D5C93}"/>
-    <hyperlink ref="AY47" r:id="rId91" xr:uid="{4A19C8E5-8DC9-2244-9B7A-DFF133598171}"/>
-    <hyperlink ref="AY49" r:id="rId92" xr:uid="{00A98B21-CE4E-F647-8D26-AD313B701E27}"/>
-    <hyperlink ref="AY70" r:id="rId93" xr:uid="{7E02BA1D-6B21-D744-89C9-DFD8DCEF1A5F}"/>
-    <hyperlink ref="AY57" r:id="rId94" xr:uid="{9581E871-6CAC-644D-9095-048B13A794A7}"/>
-    <hyperlink ref="AY58" r:id="rId95" xr:uid="{1EA1FB66-562C-554F-A505-9BFA46852FC8}"/>
-    <hyperlink ref="AX69" r:id="rId96" xr:uid="{748732B9-0DE4-7646-A18C-6A1679407E95}"/>
-    <hyperlink ref="AX38" r:id="rId97" xr:uid="{E36BC834-9005-8440-8821-FA488151234C}"/>
-    <hyperlink ref="AX35" r:id="rId98" xr:uid="{177492E4-003B-8147-A453-B13DA77CFD3C}"/>
-    <hyperlink ref="AX37" r:id="rId99" xr:uid="{DFCFD8C7-6C85-9347-A4BC-7F1D71C57408}"/>
-    <hyperlink ref="AX34" r:id="rId100" xr:uid="{4BB8D40B-2169-6A4A-99D2-79805F513C89}"/>
-    <hyperlink ref="AX36" r:id="rId101" xr:uid="{38D9667A-6B3B-5E47-A983-C1EC690553CB}"/>
-    <hyperlink ref="AX64" r:id="rId102" xr:uid="{22E910B8-805C-4742-9546-B50E37BB4BCA}"/>
-    <hyperlink ref="AX65" r:id="rId103" xr:uid="{DB15978D-EAE0-C646-9CB6-EF9193C86E5C}"/>
+    <hyperlink ref="AY71" r:id="rId73" xr:uid="{89DAE256-4128-0145-A255-6924C174EDCC}"/>
+    <hyperlink ref="AY80" r:id="rId74" xr:uid="{0C77A8D2-0A3C-B049-A707-50BFDC557AFF}"/>
+    <hyperlink ref="AY82" r:id="rId75" xr:uid="{3C4B76E8-DC03-5946-B433-B6E6DF9E13DD}"/>
+    <hyperlink ref="AY43" r:id="rId76" xr:uid="{62B9CB02-CB45-5345-BCC0-B7C0743D6392}"/>
+    <hyperlink ref="AY42" r:id="rId77" xr:uid="{FB8530CA-AD1F-3F41-A66B-66746B5A720E}"/>
+    <hyperlink ref="AY76" r:id="rId78" xr:uid="{F9A75549-C163-0B42-99F0-71AB86FF5E06}"/>
+    <hyperlink ref="AY53" r:id="rId79" xr:uid="{A1F2FF69-8941-914C-839B-08031197B516}"/>
+    <hyperlink ref="AY52" r:id="rId80" xr:uid="{7208A52F-430D-A547-98D0-C1DB4F636213}"/>
+    <hyperlink ref="AY63" r:id="rId81" xr:uid="{137EF245-936B-9540-A418-79D16D3EE056}"/>
+    <hyperlink ref="AY60" r:id="rId82" xr:uid="{B07A9345-06E3-7149-AC74-45BF02F75D6A}"/>
+    <hyperlink ref="AY45" r:id="rId83" xr:uid="{0330CE9D-13B2-0E4B-A278-85167FC1074F}"/>
+    <hyperlink ref="AY72" r:id="rId84" xr:uid="{061B6DEF-8033-AC48-BB6F-B07E0F497B13}"/>
+    <hyperlink ref="AY51" r:id="rId85" xr:uid="{7DAFB160-26AA-B44F-912E-6B8BC8A8C67D}"/>
+    <hyperlink ref="AY67" r:id="rId86" xr:uid="{0CFC5F37-67F6-7D41-8A4D-43FF8DBEE6DA}"/>
+    <hyperlink ref="AY44" r:id="rId87" xr:uid="{B70F7B97-F0FC-3046-B424-482B82129980}"/>
+    <hyperlink ref="AY78" r:id="rId88" xr:uid="{0B2889A8-B982-DE43-AC32-97640C3FC4F0}"/>
+    <hyperlink ref="AY61" r:id="rId89" xr:uid="{BB9703CE-2BEA-2E40-AB6E-E764487D5C93}"/>
+    <hyperlink ref="AY47" r:id="rId90" xr:uid="{4A19C8E5-8DC9-2244-9B7A-DFF133598171}"/>
+    <hyperlink ref="AY49" r:id="rId91" xr:uid="{00A98B21-CE4E-F647-8D26-AD313B701E27}"/>
+    <hyperlink ref="AY70" r:id="rId92" xr:uid="{7E02BA1D-6B21-D744-89C9-DFD8DCEF1A5F}"/>
+    <hyperlink ref="AY57" r:id="rId93" xr:uid="{9581E871-6CAC-644D-9095-048B13A794A7}"/>
+    <hyperlink ref="AY58" r:id="rId94" xr:uid="{1EA1FB66-562C-554F-A505-9BFA46852FC8}"/>
+    <hyperlink ref="AX69" r:id="rId95" xr:uid="{748732B9-0DE4-7646-A18C-6A1679407E95}"/>
+    <hyperlink ref="AX38" r:id="rId96" xr:uid="{E36BC834-9005-8440-8821-FA488151234C}"/>
+    <hyperlink ref="AX35" r:id="rId97" xr:uid="{177492E4-003B-8147-A453-B13DA77CFD3C}"/>
+    <hyperlink ref="AX37" r:id="rId98" xr:uid="{DFCFD8C7-6C85-9347-A4BC-7F1D71C57408}"/>
+    <hyperlink ref="AX34" r:id="rId99" xr:uid="{4BB8D40B-2169-6A4A-99D2-79805F513C89}"/>
+    <hyperlink ref="AX36" r:id="rId100" xr:uid="{38D9667A-6B3B-5E47-A983-C1EC690553CB}"/>
+    <hyperlink ref="AX64" r:id="rId101" xr:uid="{22E910B8-805C-4742-9546-B50E37BB4BCA}"/>
+    <hyperlink ref="AX65" r:id="rId102" xr:uid="{DB15978D-EAE0-C646-9CB6-EF9193C86E5C}"/>
+    <hyperlink ref="AY35" r:id="rId103" xr:uid="{6EA12A04-8CA2-C145-8AA5-BBD35BFE2638}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E6DAB1-183A-BE44-AFE8-7863C34A4EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB1C4A5-DD4D-5742-A6B1-112CDF32E855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3101" uniqueCount="835">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="838">
   <si>
     <t>nombre</t>
   </si>
@@ -2541,6 +2541,15 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1773161315/TropicalFresh_Malacatos_intro_low_horizontall_iodt1i.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1773192980/TitosRestobar_Vilcabamba_extpg_web__qmytlt.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1773192984/TitosRestobar_Vilcabamba_identhrzt_web__zay3is.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773192992/TitosRestobar_Vilcabamba_int_web__akdfla.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773192996/TitosRestobar_Vilcabamba_intpg_web__kjcnor.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773193001/TitosRestobar_Vilcabamba_intpgiz_web__uohgo8.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773193014/TitosRestobar_Vilcabamba_prdcent_web__ihf9kt.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773193020/TitosRestobar_Vilcabamba_prddetailcent_web__z0k1ja.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773193028/TitosRestobar_Vilcabamba_prdfrnt_web__capmyy.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1773193035/TitosRestobar_Vilcabamba_prodcent_web__w0ytdh.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1773193456/DescansodelToro_Vilcabamba_intro_low_horizontal_ka3ajw.mp4</t>
   </si>
 </sst>
 </file>
@@ -13285,7 +13294,9 @@
       <c r="AX62" s="9" t="s">
         <v>589</v>
       </c>
-      <c r="AY62" s="7"/>
+      <c r="AY62" s="9" t="s">
+        <v>837</v>
+      </c>
     </row>
     <row r="63" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
@@ -14967,9 +14978,11 @@
         <v>38</v>
       </c>
       <c r="AW73" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="AX73" s="7"/>
+        <v>836</v>
+      </c>
+      <c r="AX73" s="9" t="s">
+        <v>835</v>
+      </c>
       <c r="AY73" s="7"/>
     </row>
     <row r="74" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -16451,6 +16464,8 @@
     <hyperlink ref="AX64" r:id="rId101" xr:uid="{22E910B8-805C-4742-9546-B50E37BB4BCA}"/>
     <hyperlink ref="AX65" r:id="rId102" xr:uid="{DB15978D-EAE0-C646-9CB6-EF9193C86E5C}"/>
     <hyperlink ref="AY35" r:id="rId103" xr:uid="{6EA12A04-8CA2-C145-8AA5-BBD35BFE2638}"/>
+    <hyperlink ref="AX73" r:id="rId104" xr:uid="{4428EC93-523F-A340-AAA9-99EB2175D0C6}"/>
+    <hyperlink ref="AY62" r:id="rId105" xr:uid="{6B4BE52D-B6D7-9D4F-90A4-C8D2AE9E1CA2}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB1C4A5-DD4D-5742-A6B1-112CDF32E855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619EB3C5-1DFF-3442-84F6-A16970564B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="28940" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28940" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3103" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3138" uniqueCount="850">
   <si>
     <t>nombre</t>
   </si>
@@ -437,9 +437,6 @@
     <t>Cecina Johanna</t>
   </si>
   <si>
-    <t>Comedor Cuenquita</t>
-  </si>
-  <si>
     <t>El Conquistador</t>
   </si>
   <si>
@@ -2550,12 +2547,54 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1773193456/DescansodelToro_Vilcabamba_intro_low_horizontal_ka3ajw.mp4</t>
+  </si>
+  <si>
+    <t>Potochuro</t>
+  </si>
+  <si>
+    <t>Mamá Viche</t>
+  </si>
+  <si>
+    <t>Sector Centro — Diagonal al GAD Parroquial</t>
+  </si>
+  <si>
+    <t>" xiomaratorresherrera@gmail.com"</t>
+  </si>
+  <si>
+    <t>Vicenta Lima Quezada</t>
+  </si>
+  <si>
+    <t>Lavamanos funcional, Jabón Líquido, Toallas descartables, Agua Potable, Servicio higiénico, Alcohol</t>
+  </si>
+  <si>
+    <t>Teléfono Móvil, Wifi, Audio Visuales,Música ambiental</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/profile.php?id=100063626857472</t>
+  </si>
+  <si>
+    <t>https://www.instagram.com/mamaviche_/</t>
+  </si>
+  <si>
+    <t>Cocina Lojana</t>
+  </si>
+  <si>
+    <t>Cuy Asado, Gallina Cuyada, Caldo de Gallina Criolla, Cecina, Tamales.</t>
+  </si>
+  <si>
+    <t>Lunes a Domingo — 08:00 a 20:00</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -2602,7 +2641,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2638,6 +2677,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
@@ -2647,7 +2699,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2682,6 +2734,33 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3815,7 +3894,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.33203125" defaultRowHeight="20" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="42.1640625" style="1" customWidth="1"/>
@@ -3913,10 +3992,10 @@
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>13</v>
@@ -3928,40 +4007,40 @@
         <v>15</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="Y1" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="Z1" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>474</v>
       </c>
       <c r="AE1" s="2" t="s">
         <v>19</v>
@@ -3976,7 +4055,7 @@
         <v>22</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ1" s="2" t="s">
         <v>23</v>
@@ -3991,25 +4070,25 @@
         <v>26</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AO1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AP1" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="AS1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AT1" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AU1" s="2" t="s">
         <v>29</v>
@@ -4018,13 +4097,13 @@
         <v>30</v>
       </c>
       <c r="AW1" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AX1" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AY1" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2" spans="1:51" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -4038,13 +4117,13 @@
         <v>33</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E2" s="3">
         <v>979670398</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>34</v>
@@ -4059,14 +4138,14 @@
         <v>36</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O2" s="3">
         <v>1</v>
@@ -4078,25 +4157,25 @@
         <v>38</v>
       </c>
       <c r="R2" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S2" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T2" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="U2" s="4">
         <v>3.75</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W2" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="X2" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>485</v>
       </c>
       <c r="Y2" s="3">
         <v>2</v>
@@ -4169,10 +4248,10 @@
       </c>
       <c r="AV2" s="5"/>
       <c r="AW2" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AX2" s="9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AY2" s="7"/>
     </row>
@@ -4187,13 +4266,13 @@
         <v>33</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E3" s="3">
         <v>982686170</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>45</v>
@@ -4208,14 +4287,14 @@
         <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O3" s="3">
         <v>2</v>
@@ -4227,25 +4306,25 @@
         <v>38</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S3" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T3" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="U3" s="4">
         <v>2.5</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W3" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X3" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y3" s="3">
         <v>1</v>
@@ -4320,10 +4399,10 @@
         <v>38</v>
       </c>
       <c r="AW3" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="AX3" s="9" t="s">
         <v>592</v>
-      </c>
-      <c r="AX3" s="9" t="s">
-        <v>593</v>
       </c>
       <c r="AY3" s="7"/>
     </row>
@@ -4338,16 +4417,16 @@
         <v>48</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E4" s="3">
         <v>958690650</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>35</v>
@@ -4359,14 +4438,14 @@
         <v>36</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O4" s="3">
         <v>2</v>
@@ -4378,25 +4457,25 @@
         <v>38</v>
       </c>
       <c r="R4" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S4" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T4" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="U4" s="4">
         <v>3.5</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W4" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X4" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y4" s="3">
         <v>2</v>
@@ -4471,13 +4550,13 @@
         <v>38</v>
       </c>
       <c r="AW4" s="6" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AX4" s="9" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AY4" s="9" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="5" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4491,35 +4570,35 @@
         <v>48</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E5" s="3">
         <v>985094341</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O5" s="3">
         <v>2</v>
@@ -4531,25 +4610,25 @@
         <v>36</v>
       </c>
       <c r="R5" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S5" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S5" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T5" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="U5" s="4">
         <v>3</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y5" s="3">
         <v>2</v>
@@ -4624,10 +4703,10 @@
         <v>38</v>
       </c>
       <c r="AW5" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="AX5" s="9" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="AY5" s="7"/>
     </row>
@@ -4642,35 +4721,35 @@
         <v>62</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E6" s="3">
         <v>985902378</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O6" s="3">
         <v>3</v>
@@ -4682,25 +4761,25 @@
         <v>38</v>
       </c>
       <c r="R6" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S6" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T6" s="3" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="U6" s="4">
         <v>5</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Y6" s="3">
         <v>4</v>
@@ -4775,10 +4854,10 @@
         <v>38</v>
       </c>
       <c r="AW6" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AX6" s="9" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AY6" s="7"/>
     </row>
@@ -4793,35 +4872,35 @@
         <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E7" s="3">
         <v>997101647</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O7" s="3">
         <v>2</v>
@@ -4833,25 +4912,25 @@
         <v>38</v>
       </c>
       <c r="R7" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S7" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S7" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T7" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="U7" s="4">
         <v>7.5</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W7" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X7" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y7" s="3">
         <v>3</v>
@@ -4926,16 +5005,16 @@
         <v>38</v>
       </c>
       <c r="AW7" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AX7" s="9" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="AY7" s="7"/>
     </row>
     <row r="8" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
-        <v>133</v>
+        <v>837</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>32</v>
@@ -4944,35 +5023,35 @@
         <v>62</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E8" s="3">
         <v>994424295</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>57</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O8" s="3">
         <v>2</v>
@@ -4984,25 +5063,25 @@
         <v>38</v>
       </c>
       <c r="R8" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T8" s="3" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="U8" s="4">
         <v>4</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y8" s="3">
         <v>2</v>
@@ -5077,16 +5156,16 @@
         <v>38</v>
       </c>
       <c r="AW8" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AX8" s="9" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="AY8" s="7"/>
     </row>
     <row r="9" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>32</v>
@@ -5095,13 +5174,13 @@
         <v>62</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E9" s="3">
         <v>985709075</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>59</v>
@@ -5110,20 +5189,20 @@
         <v>35</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O9" s="3">
         <v>2</v>
@@ -5135,25 +5214,25 @@
         <v>38</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="U9" s="4">
         <v>6</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W9" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X9" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y9" s="3">
         <v>4</v>
@@ -5228,10 +5307,10 @@
         <v>38</v>
       </c>
       <c r="AW9" s="6" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="AX9" s="9" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AY9" s="7"/>
     </row>
@@ -5246,35 +5325,35 @@
         <v>62</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E10" s="3">
         <v>969691330</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O10" s="3">
         <v>2</v>
@@ -5286,25 +5365,25 @@
         <v>38</v>
       </c>
       <c r="R10" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T10" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="U10" s="4">
         <v>4</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y10" s="3">
         <v>3</v>
@@ -5379,16 +5458,16 @@
         <v>38</v>
       </c>
       <c r="AW10" s="6" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AX10" s="9" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AY10" s="7"/>
     </row>
     <row r="11" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>32</v>
@@ -5397,13 +5476,13 @@
         <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E11" s="3">
         <v>991450218</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>63</v>
@@ -5418,14 +5497,14 @@
         <v>36</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O11" s="3">
         <v>2</v>
@@ -5437,25 +5516,25 @@
         <v>38</v>
       </c>
       <c r="R11" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S11" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T11" s="3" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="U11" s="4">
         <v>4</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W11" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X11" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y11" s="3">
         <v>5</v>
@@ -5530,16 +5609,16 @@
         <v>38</v>
       </c>
       <c r="AW11" s="6" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="AX11" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="AY11" s="7"/>
     </row>
     <row r="12" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>32</v>
@@ -5548,13 +5627,13 @@
         <v>62</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E12" s="3">
         <v>939462796</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>64</v>
@@ -5563,20 +5642,20 @@
         <v>65</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O12" s="3">
         <v>1</v>
@@ -5588,25 +5667,25 @@
         <v>38</v>
       </c>
       <c r="R12" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S12" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T12" s="3" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="U12" s="4">
         <v>4</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W12" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="X12" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="Y12" s="3">
         <v>2</v>
@@ -5681,16 +5760,16 @@
         <v>38</v>
       </c>
       <c r="AW12" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AX12" s="9" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AY12" s="7"/>
     </row>
     <row r="13" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>32</v>
@@ -5699,22 +5778,22 @@
         <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E13" s="3">
         <v>990937330</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>65</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>36</v>
@@ -5723,11 +5802,11 @@
         <v>58</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O13" s="3">
         <v>2</v>
@@ -5739,25 +5818,25 @@
         <v>38</v>
       </c>
       <c r="R13" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S13" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T13" s="3" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="U13" s="4">
         <v>3</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y13" s="3">
         <v>3</v>
@@ -5832,16 +5911,16 @@
         <v>38</v>
       </c>
       <c r="AW13" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AX13" s="9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AY13" s="7"/>
     </row>
     <row r="14" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>32</v>
@@ -5850,35 +5929,35 @@
         <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E14" s="3">
         <v>939008806</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O14" s="3">
         <v>1</v>
@@ -5890,25 +5969,25 @@
         <v>38</v>
       </c>
       <c r="R14" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T14" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="U14" s="4">
         <v>3</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W14" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X14" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y14" s="3">
         <v>2</v>
@@ -5983,16 +6062,16 @@
         <v>38</v>
       </c>
       <c r="AW14" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AX14" s="9" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AY14" s="7"/>
     </row>
     <row r="15" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>32</v>
@@ -6001,13 +6080,13 @@
         <v>62</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E15" s="3">
         <v>985908474</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>67</v>
@@ -6025,11 +6104,11 @@
         <v>68</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O15" s="3">
         <v>3</v>
@@ -6041,25 +6120,25 @@
         <v>38</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="U15" s="4">
         <v>4</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y15" s="3">
         <v>3</v>
@@ -6134,16 +6213,16 @@
         <v>38</v>
       </c>
       <c r="AW15" s="6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="AX15" s="9" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AY15" s="7"/>
     </row>
     <row r="16" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>32</v>
@@ -6158,16 +6237,16 @@
         <v>939233599</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>36</v>
@@ -6176,13 +6255,13 @@
         <v>71</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>75</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O16" s="3">
         <v>2</v>
@@ -6194,25 +6273,25 @@
         <v>38</v>
       </c>
       <c r="R16" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S16" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T16" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="U16" s="4">
         <v>5</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y16" s="3">
         <v>3</v>
@@ -6287,10 +6366,10 @@
         <v>38</v>
       </c>
       <c r="AW16" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="AX16" s="9" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AY16" s="7"/>
     </row>
@@ -6311,7 +6390,7 @@
         <v>992586806</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>73</v>
@@ -6329,13 +6408,13 @@
         <v>74</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>75</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O17" s="3">
         <v>2</v>
@@ -6347,25 +6426,25 @@
         <v>38</v>
       </c>
       <c r="R17" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T17" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="U17" s="4">
         <v>5</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W17" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X17" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y17" s="3">
         <v>2</v>
@@ -6440,16 +6519,16 @@
         <v>38</v>
       </c>
       <c r="AW17" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AX17" s="9" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AY17" s="7"/>
     </row>
     <row r="18" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>32</v>
@@ -6461,13 +6540,13 @@
         <v>70</v>
       </c>
       <c r="E18" s="3">
-        <v>939320817</v>
+        <v>968628152</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>76</v>
@@ -6482,11 +6561,11 @@
         <v>77</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O18" s="3">
         <v>2</v>
@@ -6498,25 +6577,25 @@
         <v>38</v>
       </c>
       <c r="R18" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S18" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T18" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="U18" s="4">
         <v>5</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W18" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X18" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y18" s="3">
         <v>3</v>
@@ -6591,16 +6670,16 @@
         <v>38</v>
       </c>
       <c r="AW18" s="6" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AX18" s="9" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AY18" s="7"/>
     </row>
     <row r="19" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>32</v>
@@ -6615,10 +6694,10 @@
         <v>992309098</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>76</v>
@@ -6633,11 +6712,11 @@
         <v>78</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O19" s="3">
         <v>2</v>
@@ -6649,25 +6728,25 @@
         <v>38</v>
       </c>
       <c r="R19" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S19" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T19" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="U19" s="4">
         <v>5</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y19" s="3">
         <v>7</v>
@@ -6742,16 +6821,16 @@
         <v>38</v>
       </c>
       <c r="AW19" s="6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="AX19" s="9" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AY19" s="7"/>
     </row>
     <row r="20" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>32</v>
@@ -6760,16 +6839,16 @@
         <v>62</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E20" s="3">
-        <v>981952323</v>
+        <v>981652323</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>76</v>
@@ -6784,13 +6863,13 @@
         <v>78</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>75</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O20" s="3">
         <v>2</v>
@@ -6802,25 +6881,25 @@
         <v>38</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="U20" s="4">
         <v>5</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W20" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X20" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y20" s="3">
         <v>2</v>
@@ -6895,16 +6974,16 @@
         <v>38</v>
       </c>
       <c r="AW20" s="6" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="AX20" s="9" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AY20" s="7"/>
     </row>
     <row r="21" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>32</v>
@@ -6919,10 +6998,10 @@
         <v>939998896</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>35</v>
@@ -6937,11 +7016,11 @@
         <v>78</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O21" s="3">
         <v>2</v>
@@ -6953,25 +7032,25 @@
         <v>38</v>
       </c>
       <c r="R21" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T21" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="U21" s="4">
         <v>5</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y21" s="3">
         <v>4</v>
@@ -7046,16 +7125,16 @@
         <v>38</v>
       </c>
       <c r="AW21" s="6" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="AX21" s="9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AY21" s="7"/>
     </row>
     <row r="22" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>32</v>
@@ -7064,16 +7143,16 @@
         <v>62</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E22" s="3">
         <v>988275571</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>35</v>
@@ -7088,11 +7167,11 @@
         <v>58</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O22" s="3">
         <v>2</v>
@@ -7104,25 +7183,25 @@
         <v>38</v>
       </c>
       <c r="R22" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T22" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="U22" s="4">
         <v>4</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y22" s="3">
         <v>2</v>
@@ -7197,16 +7276,16 @@
         <v>38</v>
       </c>
       <c r="AW22" s="6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AX22" s="9" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AY22" s="7"/>
     </row>
     <row r="23" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>32</v>
@@ -7221,7 +7300,7 @@
         <v>993179418</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>79</v>
@@ -7239,11 +7318,11 @@
         <v>80</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O23" s="3">
         <v>2</v>
@@ -7255,25 +7334,25 @@
         <v>38</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="U23" s="4">
         <v>5</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y23" s="3">
         <v>2</v>
@@ -7312,7 +7391,7 @@
         <v>3</v>
       </c>
       <c r="AK23" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AL23" s="3" t="s">
         <v>42</v>
@@ -7336,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="AS23" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AT23" s="3" t="s">
         <v>44</v>
@@ -7348,16 +7427,16 @@
         <v>38</v>
       </c>
       <c r="AW23" s="6" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AX23" s="9" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="AY23" s="7"/>
     </row>
     <row r="24" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>32</v>
@@ -7366,16 +7445,16 @@
         <v>62</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E24" s="3">
         <v>992121769</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>57</v>
@@ -7390,11 +7469,11 @@
         <v>82</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O24" s="3">
         <v>2</v>
@@ -7406,25 +7485,25 @@
         <v>38</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="U24" s="4">
         <v>3</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y24" s="3">
         <v>3</v>
@@ -7499,16 +7578,16 @@
         <v>38</v>
       </c>
       <c r="AW24" s="6" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AX24" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="AY24" s="7"/>
     </row>
     <row r="25" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>32</v>
@@ -7517,22 +7596,22 @@
         <v>62</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E25" s="3">
         <v>986709948</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>36</v>
@@ -7541,11 +7620,11 @@
         <v>54</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O25" s="3">
         <v>2</v>
@@ -7557,25 +7636,25 @@
         <v>38</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S25" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S25" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T25" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="U25" s="4">
         <v>3</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Y25" s="3">
         <v>3</v>
@@ -7650,16 +7729,16 @@
         <v>38</v>
       </c>
       <c r="AW25" s="6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AX25" s="9" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AY25" s="7"/>
     </row>
     <row r="26" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>32</v>
@@ -7668,13 +7747,13 @@
         <v>62</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E26" s="3">
         <v>982944163</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>84</v>
@@ -7692,11 +7771,11 @@
         <v>54</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O26" s="3">
         <v>5</v>
@@ -7708,25 +7787,25 @@
         <v>38</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="U26" s="4">
         <v>3</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y26" s="3">
         <v>5</v>
@@ -7801,10 +7880,10 @@
         <v>38</v>
       </c>
       <c r="AW26" s="6" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AX26" s="9" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AY26" s="7"/>
     </row>
@@ -7819,13 +7898,13 @@
         <v>62</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E27" s="3">
         <v>939468990</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>86</v>
@@ -7843,11 +7922,11 @@
         <v>58</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O27" s="3">
         <v>2</v>
@@ -7859,25 +7938,25 @@
         <v>38</v>
       </c>
       <c r="R27" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T27" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="U27" s="4">
         <v>4</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y27" s="3">
         <v>4</v>
@@ -7952,16 +8031,16 @@
         <v>38</v>
       </c>
       <c r="AW27" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AX27" s="9" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="AY27" s="7"/>
     </row>
     <row r="28" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>32</v>
@@ -7970,16 +8049,16 @@
         <v>62</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E28" s="3">
         <v>980904460</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>35</v>
@@ -7994,13 +8073,13 @@
         <v>58</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="N28" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O28" s="3">
         <v>4</v>
@@ -8012,25 +8091,25 @@
         <v>36</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="U28" s="4">
         <v>4</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y28" s="3">
         <v>2</v>
@@ -8105,16 +8184,16 @@
         <v>38</v>
       </c>
       <c r="AW28" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AX28" s="9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AY28" s="7"/>
     </row>
     <row r="29" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>32</v>
@@ -8129,16 +8208,16 @@
         <v>993041863</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>36</v>
@@ -8147,11 +8226,11 @@
         <v>88</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M29" s="3"/>
       <c r="N29" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="O29" s="3">
         <v>2</v>
@@ -8163,25 +8242,25 @@
         <v>38</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="U29" s="4">
         <v>3</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W29" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="X29" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="Y29" s="3">
         <v>1</v>
@@ -8256,16 +8335,16 @@
         <v>38</v>
       </c>
       <c r="AW29" s="6" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="AX29" s="9" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AY29" s="7"/>
     </row>
     <row r="30" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>32</v>
@@ -8280,16 +8359,16 @@
         <v>994108661</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>76</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>36</v>
@@ -8298,11 +8377,11 @@
         <v>37</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="O30" s="3">
         <v>1</v>
@@ -8314,25 +8393,25 @@
         <v>38</v>
       </c>
       <c r="R30" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S30" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S30" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T30" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="U30" s="4">
         <v>3</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y30" s="3">
         <v>3</v>
@@ -8407,16 +8486,16 @@
         <v>38</v>
       </c>
       <c r="AW30" s="6" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AX30" s="9" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AY30" s="7"/>
     </row>
     <row r="31" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>32</v>
@@ -8431,10 +8510,10 @@
         <v>967437524</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>35</v>
@@ -8449,11 +8528,11 @@
         <v>37</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M31" s="3"/>
       <c r="N31" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O31" s="3">
         <v>2</v>
@@ -8465,25 +8544,25 @@
         <v>38</v>
       </c>
       <c r="R31" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S31" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S31" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T31" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="U31" s="4">
         <v>3</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y31" s="3">
         <v>3</v>
@@ -8558,16 +8637,16 @@
         <v>38</v>
       </c>
       <c r="AW31" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AX31" s="9" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="AY31" s="7"/>
     </row>
     <row r="32" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>32</v>
@@ -8582,10 +8661,10 @@
         <v>967078713</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>76</v>
@@ -8600,11 +8679,11 @@
         <v>90</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O32" s="3">
         <v>1</v>
@@ -8616,25 +8695,25 @@
         <v>38</v>
       </c>
       <c r="R32" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T32" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="U32" s="4">
         <v>3</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y32" s="3">
         <v>1</v>
@@ -8709,16 +8788,16 @@
         <v>38</v>
       </c>
       <c r="AW32" s="6" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AX32" s="9" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AY32" s="7"/>
     </row>
     <row r="33" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>83</v>
@@ -8733,16 +8812,16 @@
         <v>985550956</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>36</v>
@@ -8751,11 +8830,11 @@
         <v>90</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="M33" s="3"/>
       <c r="N33" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O33" s="3">
         <v>1</v>
@@ -8767,25 +8846,25 @@
         <v>38</v>
       </c>
       <c r="R33" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S33" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T33" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="U33" s="4">
         <v>3</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y33" s="3">
         <v>2</v>
@@ -8860,10 +8939,10 @@
         <v>38</v>
       </c>
       <c r="AW33" s="6" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AX33" s="9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AY33" s="7"/>
     </row>
@@ -8884,7 +8963,7 @@
         <v>992305288</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>94</v>
@@ -8899,14 +8978,14 @@
         <v>36</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="O34" s="3">
         <v>5</v>
@@ -8918,25 +8997,25 @@
         <v>38</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="U34" s="4">
         <v>3</v>
       </c>
       <c r="V34" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="W34" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="X34" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="W34" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="X34" s="3" t="s">
-        <v>512</v>
       </c>
       <c r="Y34" s="3">
         <v>1</v>
@@ -9011,10 +9090,10 @@
         <v>38</v>
       </c>
       <c r="AW34" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AX34" s="9" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AY34" s="7"/>
     </row>
@@ -9035,7 +9114,7 @@
         <v>9599997990</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>96</v>
@@ -9050,14 +9129,14 @@
         <v>36</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M35" s="3"/>
       <c r="N35" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O35" s="3">
         <v>5</v>
@@ -9069,25 +9148,25 @@
         <v>38</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="U35" s="4">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W35" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y35" s="3">
         <v>1</v>
@@ -9162,18 +9241,18 @@
         <v>38</v>
       </c>
       <c r="AW35" s="6" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="AX35" s="9" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="AY35" s="9" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="36" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>32</v>
@@ -9188,10 +9267,10 @@
         <v>939780206</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>35</v>
@@ -9203,14 +9282,14 @@
         <v>36</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="M36" s="3"/>
       <c r="N36" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O36" s="3">
         <v>5</v>
@@ -9222,25 +9301,25 @@
         <v>38</v>
       </c>
       <c r="R36" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="S36" s="3" t="s">
-        <v>518</v>
-      </c>
       <c r="T36" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U36" s="4">
         <v>7</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W36" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Y36" s="3">
         <v>3</v>
@@ -9315,10 +9394,10 @@
         <v>38</v>
       </c>
       <c r="AW36" s="6" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AX36" s="9" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AY36" s="7"/>
     </row>
@@ -9339,10 +9418,10 @@
         <v>998313039</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>65</v>
@@ -9354,14 +9433,14 @@
         <v>36</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M37" s="3"/>
       <c r="N37" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O37" s="3">
         <v>2</v>
@@ -9373,25 +9452,25 @@
         <v>38</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="U37" s="4">
         <v>3.5</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W37" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Y37" s="3">
         <v>3</v>
@@ -9466,16 +9545,16 @@
         <v>38</v>
       </c>
       <c r="AW37" s="6" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AX37" s="9" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="AY37" s="7"/>
     </row>
     <row r="38" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>32</v>
@@ -9490,10 +9569,10 @@
         <v>959024149</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>35</v>
@@ -9505,14 +9584,14 @@
         <v>36</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O38" s="3">
         <v>2</v>
@@ -9524,25 +9603,25 @@
         <v>38</v>
       </c>
       <c r="R38" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S38" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T38" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="U38" s="4">
         <v>3.5</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W38" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y38" s="3">
         <v>3</v>
@@ -9578,7 +9657,7 @@
         <v>41</v>
       </c>
       <c r="AJ38" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AK38" s="3" t="s">
         <v>36</v>
@@ -9602,7 +9681,7 @@
         <v>36</v>
       </c>
       <c r="AR38" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AS38" s="3" t="s">
         <v>36</v>
@@ -9617,18 +9696,18 @@
         <v>38</v>
       </c>
       <c r="AW38" s="6" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AX38" s="9" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="AY38" s="9" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="39" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>32</v>
@@ -9643,10 +9722,10 @@
         <v>991276907</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>35</v>
@@ -9658,14 +9737,14 @@
         <v>36</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O39" s="3">
         <v>3</v>
@@ -9677,25 +9756,25 @@
         <v>36</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="U39" s="4">
         <v>2</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W39" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y39" s="3">
         <v>2</v>
@@ -9770,16 +9849,16 @@
         <v>38</v>
       </c>
       <c r="AW39" s="6" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="AX39" s="9" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AY39" s="7"/>
     </row>
     <row r="40" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>32</v>
@@ -9794,7 +9873,7 @@
         <v>969349587</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>102</v>
@@ -9803,7 +9882,7 @@
         <v>35</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>36</v>
@@ -9812,11 +9891,11 @@
         <v>90</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O40" s="3">
         <v>1</v>
@@ -9828,25 +9907,25 @@
         <v>38</v>
       </c>
       <c r="R40" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S40" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T40" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="U40" s="4">
         <v>3</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W40" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X40" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X40" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y40" s="3">
         <v>2</v>
@@ -9921,16 +10000,16 @@
         <v>38</v>
       </c>
       <c r="AW40" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AX40" s="9" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="AY40" s="7"/>
     </row>
     <row r="41" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>36</v>
@@ -9945,7 +10024,7 @@
         <v>981670898</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>103</v>
@@ -9954,7 +10033,7 @@
         <v>35</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>36</v>
@@ -9963,11 +10042,11 @@
         <v>90</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O41" s="3">
         <v>2</v>
@@ -9979,25 +10058,25 @@
         <v>38</v>
       </c>
       <c r="R41" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S41" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T41" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="U41" s="4">
         <v>3</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W41" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X41" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y41" s="3">
         <v>2</v>
@@ -10072,10 +10151,10 @@
         <v>38</v>
       </c>
       <c r="AW41" s="6" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AX41" s="9" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AY41" s="7"/>
     </row>
@@ -10090,16 +10169,16 @@
         <v>101</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E42" s="3">
         <v>991347799</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>35</v>
@@ -10114,13 +10193,13 @@
         <v>105</v>
       </c>
       <c r="L42" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="M42" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>525</v>
-      </c>
       <c r="N42" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="O42" s="3">
         <v>2</v>
@@ -10132,25 +10211,25 @@
         <v>38</v>
       </c>
       <c r="R42" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S42" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T42" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="U42" s="4">
         <v>7</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y42" s="3">
         <v>3</v>
@@ -10189,13 +10268,13 @@
         <v>16</v>
       </c>
       <c r="AK42" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AL42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM42" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AN42" s="3" t="s">
         <v>32</v>
@@ -10213,7 +10292,7 @@
         <v>5</v>
       </c>
       <c r="AS42" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AT42" s="3" t="s">
         <v>106</v>
@@ -10225,13 +10304,13 @@
         <v>38</v>
       </c>
       <c r="AW42" s="6" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AX42" s="9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AY42" s="9" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="43" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10245,16 +10324,16 @@
         <v>101</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E43" s="3">
         <v>997194675</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>35</v>
@@ -10269,13 +10348,13 @@
         <v>108</v>
       </c>
       <c r="L43" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="M43" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>527</v>
-      </c>
       <c r="N43" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="O43" s="3">
         <v>5</v>
@@ -10287,25 +10366,25 @@
         <v>38</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="U43" s="4">
         <v>8</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W43" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y43" s="3">
         <v>3</v>
@@ -10344,13 +10423,13 @@
         <v>5</v>
       </c>
       <c r="AK43" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM43" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AN43" s="3" t="s">
         <v>32</v>
@@ -10368,7 +10447,7 @@
         <v>3</v>
       </c>
       <c r="AS43" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AT43" s="3" t="s">
         <v>106</v>
@@ -10380,18 +10459,18 @@
         <v>38</v>
       </c>
       <c r="AW43" s="6" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AX43" s="9" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AY43" s="9" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="44" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>32</v>
@@ -10406,7 +10485,7 @@
         <v>962983944</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>110</v>
@@ -10421,14 +10500,14 @@
         <v>36</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O44" s="3">
         <v>6</v>
@@ -10440,25 +10519,25 @@
         <v>38</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U44" s="4">
         <v>5.5</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Y44" s="3">
         <v>10</v>
@@ -10497,13 +10576,13 @@
         <v>6</v>
       </c>
       <c r="AK44" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AL44" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM44" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AN44" s="3" t="s">
         <v>83</v>
@@ -10533,18 +10612,18 @@
         <v>38</v>
       </c>
       <c r="AW44" s="6" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AX44" s="9" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AY44" s="9" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="45" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>32</v>
@@ -10559,7 +10638,7 @@
         <v>989524512</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>113</v>
@@ -10574,14 +10653,14 @@
         <v>36</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O45" s="3">
         <v>5</v>
@@ -10593,25 +10672,25 @@
         <v>38</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="U45" s="4">
         <v>5</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Y45" s="3">
         <v>3</v>
@@ -10650,13 +10729,13 @@
         <v>3</v>
       </c>
       <c r="AK45" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AL45" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM45" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AN45" s="3" t="s">
         <v>32</v>
@@ -10686,13 +10765,13 @@
         <v>38</v>
       </c>
       <c r="AW45" s="6" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="AX45" s="7" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AY45" s="9" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="46" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10712,7 +10791,7 @@
         <v>959569399</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>115</v>
@@ -10727,14 +10806,14 @@
         <v>36</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O46" s="3">
         <v>10</v>
@@ -10746,25 +10825,25 @@
         <v>38</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U46" s="4">
         <v>7</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Y46" s="3">
         <v>4</v>
@@ -10803,7 +10882,7 @@
         <v>4</v>
       </c>
       <c r="AK46" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AL46" s="3" t="s">
         <v>46</v>
@@ -10839,14 +10918,14 @@
         <v>38</v>
       </c>
       <c r="AW46" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AX46" s="7"/>
       <c r="AY46" s="7"/>
     </row>
     <row r="47" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>32</v>
@@ -10861,7 +10940,7 @@
         <v>72640148</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>116</v>
@@ -10876,16 +10955,16 @@
         <v>36</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="N47" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O47" s="3">
         <v>6</v>
@@ -10897,25 +10976,25 @@
         <v>38</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="U47" s="4">
         <v>10.5</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W47" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="X47" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="Y47" s="3">
         <v>4</v>
@@ -10954,13 +11033,13 @@
         <v>10</v>
       </c>
       <c r="AK47" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AL47" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM47" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AN47" s="3" t="s">
         <v>32</v>
@@ -10990,13 +11069,13 @@
         <v>38</v>
       </c>
       <c r="AW47" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AX47" s="9" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="AY47" s="9" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="48" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
@@ -11016,10 +11095,10 @@
         <v>992250697</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>35</v>
@@ -11034,13 +11113,13 @@
         <v>118</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="N48" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O48" s="3">
         <v>3</v>
@@ -11052,25 +11131,25 @@
         <v>38</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="U48" s="4">
         <v>3.5</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Y48" s="3">
         <v>3</v>
@@ -11109,7 +11188,7 @@
         <v>15</v>
       </c>
       <c r="AK48" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AL48" s="3" t="s">
         <v>46</v>
@@ -11145,10 +11224,10 @@
         <v>38</v>
       </c>
       <c r="AW48" s="6" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AX48" s="9" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AY48" s="7"/>
     </row>
@@ -11169,7 +11248,7 @@
         <v>960288270</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>120</v>
@@ -11184,16 +11263,16 @@
         <v>36</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="L49" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="M49" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>540</v>
-      </c>
       <c r="N49" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O49" s="3">
         <v>7</v>
@@ -11205,25 +11284,25 @@
         <v>38</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="U49" s="4">
         <v>5</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W49" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="X49" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="Y49" s="3">
         <v>3</v>
@@ -11262,13 +11341,13 @@
         <v>4</v>
       </c>
       <c r="AK49" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM49" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AN49" s="3" t="s">
         <v>32</v>
@@ -11283,10 +11362,10 @@
         <v>36</v>
       </c>
       <c r="AR49" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AS49" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AT49" s="3" t="s">
         <v>44</v>
@@ -11298,18 +11377,18 @@
         <v>38</v>
       </c>
       <c r="AW49" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AX49" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="AY49" s="9" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="50" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>32</v>
@@ -11324,10 +11403,10 @@
         <v>988271410</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>35</v>
@@ -11339,14 +11418,14 @@
         <v>36</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O50" s="3">
         <v>3</v>
@@ -11358,25 +11437,25 @@
         <v>36</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="U50" s="4">
         <v>3.5</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="Y50" s="3">
         <v>3</v>
@@ -11451,16 +11530,16 @@
         <v>38</v>
       </c>
       <c r="AW50" s="6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AX50" s="9" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="AY50" s="7"/>
     </row>
     <row r="51" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>32</v>
@@ -11475,7 +11554,7 @@
         <v>992670070</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>121</v>
@@ -11490,14 +11569,14 @@
         <v>36</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="O51" s="3">
         <v>4</v>
@@ -11509,25 +11588,25 @@
         <v>36</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="U51" s="4">
         <v>4</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y51" s="3">
         <v>1</v>
@@ -11566,13 +11645,13 @@
         <v>8</v>
       </c>
       <c r="AK51" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AL51" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM51" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AN51" s="3" t="s">
         <v>32</v>
@@ -11602,18 +11681,18 @@
         <v>38</v>
       </c>
       <c r="AW51" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="AX51" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="AY51" s="9" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="52" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>32</v>
@@ -11628,10 +11707,10 @@
         <v>939767460</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>35</v>
@@ -11643,14 +11722,14 @@
         <v>36</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O52" s="3">
         <v>5</v>
@@ -11662,25 +11741,25 @@
         <v>36</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U52" s="4">
         <v>7</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W52" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Y52" s="3">
         <v>7</v>
@@ -11719,13 +11798,13 @@
         <v>4</v>
       </c>
       <c r="AK52" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AL52" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM52" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AN52" s="3" t="s">
         <v>32</v>
@@ -11755,18 +11834,18 @@
         <v>38</v>
       </c>
       <c r="AW52" s="6" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AX52" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AY52" s="9" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="53" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>32</v>
@@ -11781,10 +11860,10 @@
         <v>991364262</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>57</v>
@@ -11799,11 +11878,11 @@
         <v>123</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O53" s="3">
         <v>6</v>
@@ -11815,25 +11894,25 @@
         <v>38</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="U53" s="4">
         <v>3</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y53" s="3">
         <v>2</v>
@@ -11872,7 +11951,7 @@
         <v>6</v>
       </c>
       <c r="AK53" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AL53" s="3" t="s">
         <v>42</v>
@@ -11908,18 +11987,18 @@
         <v>38</v>
       </c>
       <c r="AW53" s="6" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="AX53" s="9" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AY53" s="9" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="54" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>32</v>
@@ -11934,7 +12013,7 @@
         <v>72735773</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>125</v>
@@ -11949,14 +12028,14 @@
         <v>36</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O54" s="3">
         <v>3</v>
@@ -11968,25 +12047,25 @@
         <v>36</v>
       </c>
       <c r="R54" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S54" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T54" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="U54" s="4">
         <v>3</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W54" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Y54" s="3">
         <v>7</v>
@@ -12061,16 +12140,16 @@
         <v>38</v>
       </c>
       <c r="AW54" s="6" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AX54" s="9" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AY54" s="7"/>
     </row>
     <row r="55" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>32</v>
@@ -12085,10 +12164,10 @@
         <v>979802166</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>35</v>
@@ -12100,14 +12179,14 @@
         <v>36</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O55" s="3">
         <v>2</v>
@@ -12119,25 +12198,25 @@
         <v>36</v>
       </c>
       <c r="R55" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S55" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S55" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T55" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U55" s="4">
         <v>3</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W55" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y55" s="3">
         <v>3</v>
@@ -12212,16 +12291,16 @@
         <v>38</v>
       </c>
       <c r="AW55" s="6" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AX55" s="9" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AY55" s="7"/>
     </row>
     <row r="56" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>32</v>
@@ -12236,10 +12315,10 @@
         <v>996259401</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>35</v>
@@ -12251,14 +12330,14 @@
         <v>36</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M56" s="3"/>
       <c r="N56" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O56" s="3">
         <v>2</v>
@@ -12270,25 +12349,25 @@
         <v>36</v>
       </c>
       <c r="R56" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S56" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S56" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T56" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="U56" s="4">
         <v>2.75</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W56" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Y56" s="3">
         <v>3</v>
@@ -12363,16 +12442,16 @@
         <v>38</v>
       </c>
       <c r="AW56" s="6" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AX56" s="9" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AY56" s="7"/>
     </row>
     <row r="57" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>32</v>
@@ -12387,10 +12466,10 @@
         <v>990716673</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>35</v>
@@ -12402,16 +12481,16 @@
         <v>36</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N57" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O57" s="3">
         <v>4</v>
@@ -12423,25 +12502,25 @@
         <v>38</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="U57" s="4">
         <v>5</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W57" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="X57" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="Y57" s="3">
         <v>2</v>
@@ -12477,16 +12556,16 @@
         <v>41</v>
       </c>
       <c r="AJ57" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AK57" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AL57" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM57" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AN57" s="3" t="s">
         <v>83</v>
@@ -12501,7 +12580,7 @@
         <v>36</v>
       </c>
       <c r="AR57" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AS57" s="3" t="s">
         <v>36</v>
@@ -12516,18 +12595,18 @@
         <v>38</v>
       </c>
       <c r="AW57" s="6" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AX57" s="9" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AY57" s="9" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="58" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>32</v>
@@ -12542,10 +12621,10 @@
         <v>988637307</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>35</v>
@@ -12557,16 +12636,16 @@
         <v>36</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L58" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="M58" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>549</v>
-      </c>
       <c r="N58" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O58" s="3">
         <v>1</v>
@@ -12575,28 +12654,28 @@
         <v>40</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="U58" s="4">
         <v>5.5</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W58" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Y58" s="3">
         <v>3</v>
@@ -12635,13 +12714,13 @@
         <v>4</v>
       </c>
       <c r="AK58" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AL58" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM58" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AN58" s="3" t="s">
         <v>32</v>
@@ -12671,13 +12750,13 @@
         <v>38</v>
       </c>
       <c r="AW58" s="6" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="AX58" s="9" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AY58" s="9" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="59" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12697,10 +12776,10 @@
         <v>969647354</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>35</v>
@@ -12712,16 +12791,16 @@
         <v>36</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O59" s="3">
         <v>4</v>
@@ -12730,28 +12809,28 @@
         <v>30</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U59" s="4">
         <v>5</v>
       </c>
       <c r="V59" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W59" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="X59" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="Y59" s="3">
         <v>2</v>
@@ -12790,7 +12869,7 @@
         <v>4</v>
       </c>
       <c r="AK59" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AL59" s="3" t="s">
         <v>42</v>
@@ -12826,16 +12905,16 @@
         <v>38</v>
       </c>
       <c r="AW59" s="6" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="AX59" s="9" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AY59" s="7"/>
     </row>
     <row r="60" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>36</v>
@@ -12844,16 +12923,16 @@
         <v>109</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E60" s="3">
         <v>939385851</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>35</v>
@@ -12868,13 +12947,13 @@
         <v>88</v>
       </c>
       <c r="L60" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="M60" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>553</v>
-      </c>
       <c r="N60" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O60" s="3">
         <v>2</v>
@@ -12886,25 +12965,25 @@
         <v>38</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="U60" s="4">
         <v>5</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W60" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="X60" s="3" t="s">
         <v>496</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="Y60" s="3">
         <v>3</v>
@@ -12943,13 +13022,13 @@
         <v>4</v>
       </c>
       <c r="AK60" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AL60" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM60" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AN60" s="3" t="s">
         <v>32</v>
@@ -12967,7 +13046,7 @@
         <v>6</v>
       </c>
       <c r="AS60" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AT60" s="3" t="s">
         <v>106</v>
@@ -12979,18 +13058,18 @@
         <v>38</v>
       </c>
       <c r="AW60" s="6" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AX60" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AY60" s="9" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="61" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>32</v>
@@ -12999,16 +13078,16 @@
         <v>109</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E61" s="3">
         <v>989804020</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>35</v>
@@ -13020,16 +13099,16 @@
         <v>36</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L61" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="M61" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="M61" s="3" t="s">
-        <v>556</v>
-      </c>
       <c r="N61" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O61" s="3">
         <v>4</v>
@@ -13041,25 +13120,25 @@
         <v>38</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="U61" s="4">
         <v>8</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W61" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y61" s="3">
         <v>4</v>
@@ -13098,13 +13177,13 @@
         <v>4</v>
       </c>
       <c r="AK61" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AL61" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM61" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AN61" s="3" t="s">
         <v>32</v>
@@ -13122,7 +13201,7 @@
         <v>4</v>
       </c>
       <c r="AS61" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AT61" s="3" t="s">
         <v>106</v>
@@ -13134,18 +13213,18 @@
         <v>38</v>
       </c>
       <c r="AW61" s="6" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AX61" s="7" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="AY61" s="9" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="62" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>32</v>
@@ -13154,16 +13233,16 @@
         <v>109</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E62" s="3">
         <v>980882809</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>35</v>
@@ -13175,16 +13254,16 @@
         <v>36</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="L62" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="M62" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>559</v>
-      </c>
       <c r="N62" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O62" s="3">
         <v>10</v>
@@ -13196,25 +13275,25 @@
         <v>38</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="U62" s="4">
         <v>7</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W62" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Y62" s="3">
         <v>10</v>
@@ -13253,13 +13332,13 @@
         <v>15</v>
       </c>
       <c r="AK62" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AL62" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM62" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AN62" s="3" t="s">
         <v>32</v>
@@ -13271,7 +13350,7 @@
         <v>50</v>
       </c>
       <c r="AQ62" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AR62" s="3">
         <v>3</v>
@@ -13289,18 +13368,18 @@
         <v>38</v>
       </c>
       <c r="AW62" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="AX62" s="9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="AY62" s="9" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="63" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>32</v>
@@ -13309,16 +13388,16 @@
         <v>109</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E63" s="3">
         <v>984934506</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>35</v>
@@ -13330,16 +13409,16 @@
         <v>36</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="L63" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="M63" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="M63" s="3" t="s">
-        <v>561</v>
-      </c>
       <c r="N63" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O63" s="3">
         <v>7</v>
@@ -13354,22 +13433,22 @@
         <v>98</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U63" s="4">
         <v>7</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W63" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y63" s="3">
         <v>5</v>
@@ -13408,13 +13487,13 @@
         <v>5</v>
       </c>
       <c r="AK63" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AL63" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM63" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AN63" s="3" t="s">
         <v>32</v>
@@ -13423,7 +13502,7 @@
         <v>6</v>
       </c>
       <c r="AP63" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AQ63" s="3" t="s">
         <v>36</v>
@@ -13432,7 +13511,7 @@
         <v>26</v>
       </c>
       <c r="AS63" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="AT63" s="3" t="s">
         <v>44</v>
@@ -13444,18 +13523,18 @@
         <v>38</v>
       </c>
       <c r="AW63" s="6" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AX63" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AY63" s="9" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="64" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>32</v>
@@ -13464,16 +13543,16 @@
         <v>92</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E64" s="3">
         <v>997382881</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>35</v>
@@ -13485,16 +13564,16 @@
         <v>36</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N64" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O64" s="3">
         <v>8</v>
@@ -13506,25 +13585,25 @@
         <v>38</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="U64" s="4">
         <v>5.5</v>
       </c>
       <c r="V64" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="W64" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Y64" s="3">
         <v>2</v>
@@ -13563,7 +13642,7 @@
         <v>6</v>
       </c>
       <c r="AK64" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AL64" s="3" t="s">
         <v>46</v>
@@ -13587,7 +13666,7 @@
         <v>1</v>
       </c>
       <c r="AS64" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AT64" s="3" t="s">
         <v>44</v>
@@ -13599,16 +13678,16 @@
         <v>38</v>
       </c>
       <c r="AW64" s="6" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AX64" s="9" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AY64" s="7"/>
     </row>
     <row r="65" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>32</v>
@@ -13623,10 +13702,10 @@
         <v>992714781</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>35</v>
@@ -13638,14 +13717,14 @@
         <v>36</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="M65" s="3"/>
       <c r="N65" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O65" s="3">
         <v>5</v>
@@ -13657,25 +13736,25 @@
         <v>38</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="U65" s="4">
         <v>3</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W65" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Y65" s="3">
         <v>1</v>
@@ -13714,13 +13793,13 @@
         <v>5</v>
       </c>
       <c r="AK65" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AL65" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM65" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AN65" s="3" t="s">
         <v>32</v>
@@ -13750,16 +13829,16 @@
         <v>38</v>
       </c>
       <c r="AW65" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AX65" s="9" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="AY65" s="7"/>
     </row>
     <row r="66" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>32</v>
@@ -13768,16 +13847,16 @@
         <v>109</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E66" s="3">
         <v>987192802</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>35</v>
@@ -13789,14 +13868,14 @@
         <v>36</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O66" s="3">
         <v>3</v>
@@ -13808,25 +13887,25 @@
         <v>38</v>
       </c>
       <c r="R66" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S66" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T66" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="U66" s="4">
         <v>3</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y66" s="3">
         <v>2</v>
@@ -13865,7 +13944,7 @@
         <v>16</v>
       </c>
       <c r="AK66" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AL66" s="3" t="s">
         <v>46</v>
@@ -13901,16 +13980,16 @@
         <v>38</v>
       </c>
       <c r="AW66" s="6" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="AX66" s="9" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AY66" s="7"/>
     </row>
     <row r="67" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>32</v>
@@ -13925,10 +14004,10 @@
         <v>991322614</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>35</v>
@@ -13940,14 +14019,14 @@
         <v>36</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O67" s="3">
         <v>6</v>
@@ -13959,25 +14038,25 @@
         <v>38</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="U67" s="4">
         <v>3.5</v>
       </c>
       <c r="V67" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Y67" s="3">
         <v>4</v>
@@ -14052,24 +14131,24 @@
         <v>38</v>
       </c>
       <c r="AW67" s="6" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="AX67" s="9" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AY67" s="9" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="68" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>93</v>
@@ -14078,10 +14157,10 @@
         <v>969306278</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>35</v>
@@ -14093,16 +14172,16 @@
         <v>36</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N68" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O68" s="3">
         <v>7</v>
@@ -14114,25 +14193,25 @@
         <v>38</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="U68" s="4">
         <v>5</v>
       </c>
       <c r="V68" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W68" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y68" s="3">
         <v>5</v>
@@ -14171,13 +14250,13 @@
         <v>4</v>
       </c>
       <c r="AK68" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AL68" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM68" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AN68" s="3" t="s">
         <v>32</v>
@@ -14207,18 +14286,18 @@
         <v>38</v>
       </c>
       <c r="AW68" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="AX68" s="9" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AY68" s="9" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="69" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>32</v>
@@ -14227,16 +14306,16 @@
         <v>92</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E69" s="3">
         <v>991860378</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>35</v>
@@ -14248,16 +14327,16 @@
         <v>36</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N69" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O69" s="3">
         <v>12</v>
@@ -14269,25 +14348,25 @@
         <v>38</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T69" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="U69" s="4">
         <v>5</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W69" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y69" s="3">
         <v>3</v>
@@ -14326,13 +14405,13 @@
         <v>8</v>
       </c>
       <c r="AK69" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AL69" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM69" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AN69" s="3" t="s">
         <v>32</v>
@@ -14350,7 +14429,7 @@
         <v>3</v>
       </c>
       <c r="AS69" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AT69" s="3" t="s">
         <v>44</v>
@@ -14362,18 +14441,18 @@
         <v>38</v>
       </c>
       <c r="AW69" s="6" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="AX69" s="9" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AY69" s="9" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="70" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>32</v>
@@ -14382,16 +14461,16 @@
         <v>109</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E70" s="3">
         <v>987979144</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>35</v>
@@ -14403,16 +14482,16 @@
         <v>36</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="N70" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O70" s="3">
         <v>6</v>
@@ -14424,25 +14503,25 @@
         <v>38</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="U70" s="4">
         <v>12</v>
       </c>
       <c r="V70" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W70" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y70" s="3">
         <v>2</v>
@@ -14481,13 +14560,13 @@
         <v>12</v>
       </c>
       <c r="AK70" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AL70" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM70" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AN70" s="3" t="s">
         <v>32</v>
@@ -14517,36 +14596,36 @@
         <v>38</v>
       </c>
       <c r="AW70" s="6" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AX70" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AY70" s="9" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="71" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E71" s="3">
         <v>984234395</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>35</v>
@@ -14558,16 +14637,16 @@
         <v>36</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L71" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="M71" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="M71" s="3" t="s">
-        <v>575</v>
-      </c>
       <c r="N71" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O71" s="3">
         <v>10</v>
@@ -14579,25 +14658,25 @@
         <v>38</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T71" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="U71" s="4">
         <v>10</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W71" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y71" s="3">
         <v>2</v>
@@ -14636,13 +14715,13 @@
         <v>12</v>
       </c>
       <c r="AK71" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AL71" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM71" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AN71" s="3" t="s">
         <v>32</v>
@@ -14660,7 +14739,7 @@
         <v>4</v>
       </c>
       <c r="AS71" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AT71" s="3" t="s">
         <v>106</v>
@@ -14672,18 +14751,18 @@
         <v>38</v>
       </c>
       <c r="AW71" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="AX71" s="9" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AY71" s="9" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="72" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>32</v>
@@ -14698,10 +14777,10 @@
         <v>989577107</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>57</v>
@@ -14713,14 +14792,14 @@
         <v>36</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O72" s="3">
         <v>7</v>
@@ -14732,25 +14811,25 @@
         <v>38</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T72" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="U72" s="4">
         <v>1</v>
       </c>
       <c r="V72" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="W72" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y72" s="3">
         <v>4</v>
@@ -14789,13 +14868,13 @@
         <v>20</v>
       </c>
       <c r="AK72" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AL72" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM72" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AN72" s="3" t="s">
         <v>32</v>
@@ -14825,18 +14904,18 @@
         <v>38</v>
       </c>
       <c r="AW72" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AX72" s="9" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="AY72" s="9" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="73" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>32</v>
@@ -14845,16 +14924,16 @@
         <v>109</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E73" s="3">
         <v>962876988</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>35</v>
@@ -14866,14 +14945,14 @@
         <v>36</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O73" s="3">
         <v>5</v>
@@ -14885,25 +14964,25 @@
         <v>38</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T73" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="U73" s="4">
         <v>3</v>
       </c>
       <c r="V73" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W73" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Y73" s="3">
         <v>2</v>
@@ -14948,7 +15027,7 @@
         <v>46</v>
       </c>
       <c r="AM73" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AN73" s="3" t="s">
         <v>32</v>
@@ -14978,16 +15057,16 @@
         <v>38</v>
       </c>
       <c r="AW73" s="6" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AX73" s="9" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="AY73" s="7"/>
     </row>
     <row r="74" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>32</v>
@@ -15002,10 +15081,10 @@
         <v>939866173</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>35</v>
@@ -15017,14 +15096,14 @@
         <v>36</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O74" s="3">
         <v>4</v>
@@ -15036,25 +15115,25 @@
         <v>38</v>
       </c>
       <c r="R74" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S74" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S74" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T74" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="U74" s="4">
         <v>3.5</v>
       </c>
       <c r="V74" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W74" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Y74" s="3">
         <v>2</v>
@@ -15093,7 +15172,7 @@
         <v>10</v>
       </c>
       <c r="AK74" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AL74" s="3" t="s">
         <v>46</v>
@@ -15129,16 +15208,16 @@
         <v>38</v>
       </c>
       <c r="AW74" s="6" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AX74" s="9" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AY74" s="7"/>
     </row>
     <row r="75" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>32</v>
@@ -15153,10 +15232,10 @@
         <v>986925665</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>35</v>
@@ -15168,14 +15247,14 @@
         <v>36</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="O75" s="3">
         <v>3</v>
@@ -15187,25 +15266,25 @@
         <v>38</v>
       </c>
       <c r="R75" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S75" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S75" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T75" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="U75" s="4">
         <v>2.25</v>
       </c>
       <c r="V75" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="W75" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="Y75" s="3">
         <v>3</v>
@@ -15280,16 +15359,16 @@
         <v>38</v>
       </c>
       <c r="AW75" s="6" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="AX75" s="9" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AY75" s="7"/>
     </row>
     <row r="76" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>32</v>
@@ -15298,16 +15377,16 @@
         <v>109</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E76" s="3">
         <v>985480644</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>35</v>
@@ -15319,16 +15398,16 @@
         <v>36</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N76" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O76" s="3">
         <v>5</v>
@@ -15340,25 +15419,25 @@
         <v>38</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T76" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="U76" s="4">
         <v>3.5</v>
       </c>
       <c r="V76" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W76" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y76" s="3">
         <v>3</v>
@@ -15397,13 +15476,13 @@
         <v>5</v>
       </c>
       <c r="AK76" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AL76" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM76" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AN76" s="3" t="s">
         <v>32</v>
@@ -15433,36 +15512,36 @@
         <v>38</v>
       </c>
       <c r="AW76" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="AX76" s="9" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AY76" s="9" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="77" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E77" s="3">
         <v>96262869</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>35</v>
@@ -15474,16 +15553,16 @@
         <v>36</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="N77" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O77" s="3">
         <v>3</v>
@@ -15495,25 +15574,25 @@
         <v>38</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="T77" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="U77" s="4">
         <v>6</v>
       </c>
       <c r="V77" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W77" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="Y77" s="3">
         <v>2</v>
@@ -15552,7 +15631,7 @@
         <v>9</v>
       </c>
       <c r="AK77" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AL77" s="3" t="s">
         <v>42</v>
@@ -15576,7 +15655,7 @@
         <v>2</v>
       </c>
       <c r="AS77" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AT77" s="3" t="s">
         <v>44</v>
@@ -15588,16 +15667,16 @@
         <v>38</v>
       </c>
       <c r="AW77" s="6" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="AX77" s="9" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="AY77" s="7"/>
     </row>
     <row r="78" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>83</v>
@@ -15606,16 +15685,16 @@
         <v>109</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E78" s="3">
         <v>939537782</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>35</v>
@@ -15627,14 +15706,14 @@
         <v>36</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O78" s="3">
         <v>3</v>
@@ -15646,25 +15725,25 @@
         <v>38</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T78" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="U78" s="4">
         <v>3.5</v>
       </c>
       <c r="V78" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="W78" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="Y78" s="3">
         <v>1</v>
@@ -15727,7 +15806,7 @@
         <v>1</v>
       </c>
       <c r="AS78" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AT78" s="3" t="s">
         <v>44</v>
@@ -15739,36 +15818,36 @@
         <v>38</v>
       </c>
       <c r="AW78" s="6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AX78" s="9" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AY78" s="9" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="79" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E79" s="3">
         <v>967800981</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>35</v>
@@ -15780,14 +15859,14 @@
         <v>36</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O79" s="3">
         <v>3</v>
@@ -15799,25 +15878,25 @@
         <v>38</v>
       </c>
       <c r="R79" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="S79" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S79" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="T79" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="U79" s="4">
         <v>2.5</v>
       </c>
       <c r="V79" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W79" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Y79" s="3">
         <v>1</v>
@@ -15892,34 +15971,34 @@
         <v>38</v>
       </c>
       <c r="AW79" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AX79" s="9" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AY79" s="7"/>
     </row>
     <row r="80" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E80" s="3">
         <v>995832522</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>57</v>
@@ -15931,16 +16010,16 @@
         <v>36</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="N80" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O80" s="3">
         <v>4</v>
@@ -15952,25 +16031,25 @@
         <v>38</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="S80" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T80" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="U80" s="4">
         <v>6</v>
       </c>
       <c r="V80" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="W80" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Y80" s="3">
         <v>2</v>
@@ -16045,18 +16124,18 @@
         <v>38</v>
       </c>
       <c r="AW80" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AX80" s="9" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AY80" s="9" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="81" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>32</v>
@@ -16065,16 +16144,16 @@
         <v>109</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E81" s="3">
         <v>989874633</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>65</v>
@@ -16086,16 +16165,16 @@
         <v>36</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="N81" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="O81" s="3">
         <v>5</v>
@@ -16107,25 +16186,25 @@
         <v>38</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="S81" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="T81" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="U81" s="4">
         <v>3</v>
       </c>
       <c r="V81" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="W81" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="Y81" s="3">
         <v>2</v>
@@ -16200,163 +16279,310 @@
         <v>38</v>
       </c>
       <c r="AW81" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AX81" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AY81" s="7"/>
     </row>
     <row r="82" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E82" s="3">
+      <c r="A82" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="B82" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="E82" s="12">
         <v>995832522</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="H82" s="3" t="s">
+      <c r="F82" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G82" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="H82" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="I82" s="3" t="s">
+      <c r="I82" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="J82" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="M82" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="N82" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="O82" s="3">
+      <c r="J82" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="K82" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="L82" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="M82" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="N82" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="O82" s="12">
         <v>4</v>
       </c>
-      <c r="P82" s="3">
+      <c r="P82" s="12">
         <v>40</v>
       </c>
-      <c r="Q82" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="R82" s="3" t="s">
+      <c r="Q82" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="R82" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="S82" s="12" t="s">
+        <v>517</v>
+      </c>
+      <c r="T82" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="U82" s="13">
+        <v>6</v>
+      </c>
+      <c r="V82" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="W82" s="14"/>
+      <c r="X82" s="14"/>
+      <c r="Y82" s="12">
+        <v>2</v>
+      </c>
+      <c r="Z82" s="12">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB82" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC82" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD82" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE82" s="15">
+        <v>-3.7900879999999999</v>
+      </c>
+      <c r="AF82" s="15">
+        <v>-79.287612100000004</v>
+      </c>
+      <c r="AG82" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH82" s="12">
+        <v>56</v>
+      </c>
+      <c r="AI82" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ82" s="12">
+        <v>10</v>
+      </c>
+      <c r="AK82" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="AL82" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM82" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AN82" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO82" s="12">
+        <v>8</v>
+      </c>
+      <c r="AP82" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="AQ82" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR82" s="12">
+        <v>1</v>
+      </c>
+      <c r="AS82" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="AT82" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="AU82" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV82" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="AW82" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="AX82" s="17" t="s">
+        <v>586</v>
+      </c>
+      <c r="AY82" s="9" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="83" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A83" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="E83" s="3">
+        <v>917850039</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I83" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="J83" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="M83" s="19"/>
+      <c r="N83" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="O83" s="19">
+        <v>3</v>
+      </c>
+      <c r="P83" s="19">
+        <v>50</v>
+      </c>
+      <c r="Q83" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="S83" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="S82" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="T82" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="U82" s="4">
-        <v>6</v>
-      </c>
-      <c r="V82" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="W82" s="5"/>
-      <c r="X82" s="5"/>
-      <c r="Y82" s="3">
+      <c r="T83" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="U83" s="20">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="X83" s="18" t="s">
+        <v>496</v>
+      </c>
+      <c r="Y83" s="19">
         <v>2</v>
       </c>
-      <c r="Z82" s="3">
+      <c r="Z83" s="19">
         <v>0</v>
       </c>
-      <c r="AA82" s="3" t="s">
+      <c r="AA83" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="AB82" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AC82" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="AD82" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE82" s="10">
-        <v>-3.7900879999999999</v>
-      </c>
-      <c r="AF82" s="10">
-        <v>-79.287612100000004</v>
-      </c>
-      <c r="AG82" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH82" s="3">
-        <v>56</v>
-      </c>
-      <c r="AI82" s="3" t="s">
+      <c r="AB83" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="AC83" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AD83" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE83" s="10">
+        <v>-3.8892690000000001</v>
+      </c>
+      <c r="AF83" s="10">
+        <v>-79.287571</v>
+      </c>
+      <c r="AG83" s="18" t="s">
+        <v>849</v>
+      </c>
+      <c r="AH83" s="19">
+        <v>67</v>
+      </c>
+      <c r="AI83" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="AJ82" s="3">
-        <v>10</v>
-      </c>
-      <c r="AK82" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="AL82" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM82" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AN82" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="AO82" s="3">
-        <v>8</v>
-      </c>
-      <c r="AP82" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="AQ82" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AR82" s="3">
-        <v>1</v>
-      </c>
-      <c r="AS82" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="AT82" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="AU82" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AV82" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AW82" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="AX82" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="AY82" s="9" t="s">
-        <v>796</v>
-      </c>
+      <c r="AJ83" s="19">
+        <v>12</v>
+      </c>
+      <c r="AK83" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="AL83" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="AM83" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="AN83" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO83" s="19">
+        <v>12</v>
+      </c>
+      <c r="AP83" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ83" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR83" s="19">
+        <v>5</v>
+      </c>
+      <c r="AS83" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT83" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU83" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV83" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="AW83" s="19"/>
+      <c r="AX83" s="19"/>
+      <c r="AY83" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{619EB3C5-1DFF-3442-84F6-A16970564B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482E8938-CBB2-9743-89FC-273BE1A49998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28940" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1013,12 +1013,6 @@
     <t>Lavamanos funcional, Jabón Líquido, Toallas descartables, Agua potable, Utensilios de limpieza.</t>
   </si>
   <si>
-    <t>Lavamanos funcional, Jabón Líquido, Toallas descartables, Alcohol, Utensilios de limpieza.</t>
-  </si>
-  <si>
-    <t>Lavamanos funcional, Jabón Líquido, Toallas descartables, Agua potable, Alcohol, Utensilios de limpieza.</t>
-  </si>
-  <si>
     <t>Jardin dentro del restaurante</t>
   </si>
   <si>
@@ -2586,6 +2580,12 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>Lavamanos funcional, Jabón Líquido, Toallas descartables, Servicio higiénico, Alcohol, Utensilios de limpieza.</t>
+  </si>
+  <si>
+    <t>Lavamanos funcional, Jabón Líquido, Toallas descartables, Servicio higiénico,Agua potable, Alcohol, Utensilios de limpieza.</t>
   </si>
 </sst>
 </file>
@@ -3992,10 +3992,10 @@
         <v>12</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>13</v>
@@ -4007,40 +4007,40 @@
         <v>15</v>
       </c>
       <c r="S1" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="T1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="U1" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="W1" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="X1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="Y1" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="AC1" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="AD1" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="AE1" s="2" t="s">
         <v>19</v>
@@ -4055,7 +4055,7 @@
         <v>22</v>
       </c>
       <c r="AI1" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="AJ1" s="2" t="s">
         <v>23</v>
@@ -4070,25 +4070,25 @@
         <v>26</v>
       </c>
       <c r="AN1" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="AO1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AP1" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="AR1" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="AQ1" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="AR1" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="AS1" s="2" t="s">
         <v>28</v>
       </c>
       <c r="AT1" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="AU1" s="2" t="s">
         <v>29</v>
@@ -4097,13 +4097,13 @@
         <v>30</v>
       </c>
       <c r="AW1" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AX1" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AY1" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:51" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -4138,10 +4138,10 @@
         <v>36</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="s">
@@ -4157,13 +4157,13 @@
         <v>38</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="U2" s="4">
         <v>3.75</v>
@@ -4172,10 +4172,10 @@
         <v>204</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Y2" s="3">
         <v>2</v>
@@ -4248,10 +4248,10 @@
       </c>
       <c r="AV2" s="5"/>
       <c r="AW2" s="6" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="AX2" s="9" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AY2" s="7"/>
     </row>
@@ -4287,10 +4287,10 @@
         <v>36</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3" t="s">
@@ -4306,13 +4306,13 @@
         <v>38</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="U3" s="4">
         <v>2.5</v>
@@ -4321,10 +4321,10 @@
         <v>204</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y3" s="3">
         <v>1</v>
@@ -4399,10 +4399,10 @@
         <v>38</v>
       </c>
       <c r="AW3" s="6" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AX3" s="9" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AY3" s="7"/>
     </row>
@@ -4438,10 +4438,10 @@
         <v>36</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3" t="s">
@@ -4457,13 +4457,13 @@
         <v>38</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="U4" s="4">
         <v>3.5</v>
@@ -4472,10 +4472,10 @@
         <v>204</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y4" s="3">
         <v>2</v>
@@ -4550,13 +4550,13 @@
         <v>38</v>
       </c>
       <c r="AW4" s="6" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="AX4" s="9" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="AY4" s="9" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="5" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -4585,16 +4585,16 @@
         <v>35</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3" t="s">
@@ -4610,13 +4610,13 @@
         <v>36</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T5" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="U5" s="4">
         <v>3</v>
@@ -4625,10 +4625,10 @@
         <v>204</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y5" s="3">
         <v>2</v>
@@ -4703,10 +4703,10 @@
         <v>38</v>
       </c>
       <c r="AW5" s="6" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="AX5" s="9" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="AY5" s="7"/>
     </row>
@@ -4736,16 +4736,16 @@
         <v>35</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3" t="s">
@@ -4761,13 +4761,13 @@
         <v>38</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="U6" s="4">
         <v>5</v>
@@ -4776,10 +4776,10 @@
         <v>204</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X6" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Y6" s="3">
         <v>4</v>
@@ -4854,10 +4854,10 @@
         <v>38</v>
       </c>
       <c r="AW6" s="6" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="AX6" s="9" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AY6" s="7"/>
     </row>
@@ -4887,16 +4887,16 @@
         <v>35</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3" t="s">
@@ -4912,13 +4912,13 @@
         <v>38</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="U7" s="4">
         <v>7.5</v>
@@ -4927,10 +4927,10 @@
         <v>204</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y7" s="3">
         <v>3</v>
@@ -5005,16 +5005,16 @@
         <v>38</v>
       </c>
       <c r="AW7" s="6" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AX7" s="9" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="AY7" s="7"/>
     </row>
     <row r="8" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="3" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>32</v>
@@ -5038,16 +5038,16 @@
         <v>57</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="s">
@@ -5063,13 +5063,13 @@
         <v>38</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="U8" s="4">
         <v>4</v>
@@ -5078,10 +5078,10 @@
         <v>204</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y8" s="3">
         <v>2</v>
@@ -5156,10 +5156,10 @@
         <v>38</v>
       </c>
       <c r="AW8" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="AX8" s="9" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="AY8" s="7"/>
     </row>
@@ -5189,16 +5189,16 @@
         <v>35</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3" t="s">
@@ -5214,13 +5214,13 @@
         <v>38</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T9" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="U9" s="4">
         <v>6</v>
@@ -5229,10 +5229,10 @@
         <v>204</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X9" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y9" s="3">
         <v>4</v>
@@ -5307,10 +5307,10 @@
         <v>38</v>
       </c>
       <c r="AW9" s="6" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="AX9" s="9" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AY9" s="7"/>
     </row>
@@ -5340,16 +5340,16 @@
         <v>35</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="s">
@@ -5365,13 +5365,13 @@
         <v>38</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="U10" s="4">
         <v>4</v>
@@ -5380,10 +5380,10 @@
         <v>204</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="X10" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y10" s="3">
         <v>3</v>
@@ -5458,10 +5458,10 @@
         <v>38</v>
       </c>
       <c r="AW10" s="6" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="AX10" s="9" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="AY10" s="7"/>
     </row>
@@ -5497,10 +5497,10 @@
         <v>36</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3" t="s">
@@ -5516,13 +5516,13 @@
         <v>38</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T11" s="3" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="U11" s="4">
         <v>4</v>
@@ -5531,10 +5531,10 @@
         <v>204</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y11" s="3">
         <v>5</v>
@@ -5609,10 +5609,10 @@
         <v>38</v>
       </c>
       <c r="AW11" s="6" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="AX11" s="9" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="AY11" s="7"/>
     </row>
@@ -5642,16 +5642,16 @@
         <v>65</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="s">
@@ -5667,13 +5667,13 @@
         <v>38</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="U12" s="4">
         <v>4</v>
@@ -5682,10 +5682,10 @@
         <v>204</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y12" s="3">
         <v>2</v>
@@ -5760,10 +5760,10 @@
         <v>38</v>
       </c>
       <c r="AW12" s="6" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="AX12" s="9" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AY12" s="7"/>
     </row>
@@ -5793,7 +5793,7 @@
         <v>65</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>36</v>
@@ -5802,7 +5802,7 @@
         <v>58</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3" t="s">
@@ -5818,13 +5818,13 @@
         <v>38</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T13" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="U13" s="4">
         <v>3</v>
@@ -5833,10 +5833,10 @@
         <v>204</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y13" s="3">
         <v>3</v>
@@ -5911,10 +5911,10 @@
         <v>38</v>
       </c>
       <c r="AW13" s="6" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="AX13" s="9" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="AY13" s="7"/>
     </row>
@@ -5944,7 +5944,7 @@
         <v>35</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>36</v>
@@ -5953,7 +5953,7 @@
         <v>297</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3" t="s">
@@ -5969,13 +5969,13 @@
         <v>38</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="U14" s="4">
         <v>3</v>
@@ -5984,10 +5984,10 @@
         <v>204</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y14" s="3">
         <v>2</v>
@@ -6062,10 +6062,10 @@
         <v>38</v>
       </c>
       <c r="AW14" s="6" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="AX14" s="9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="AY14" s="7"/>
     </row>
@@ -6104,7 +6104,7 @@
         <v>68</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3" t="s">
@@ -6120,13 +6120,13 @@
         <v>38</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T15" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="U15" s="4">
         <v>4</v>
@@ -6135,10 +6135,10 @@
         <v>204</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X15" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y15" s="3">
         <v>3</v>
@@ -6213,10 +6213,10 @@
         <v>38</v>
       </c>
       <c r="AW15" s="6" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="AX15" s="9" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="AY15" s="7"/>
     </row>
@@ -6246,7 +6246,7 @@
         <v>35</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>36</v>
@@ -6255,7 +6255,7 @@
         <v>71</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>75</v>
@@ -6273,25 +6273,25 @@
         <v>38</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="U16" s="4">
         <v>5</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y16" s="3">
         <v>3</v>
@@ -6366,10 +6366,10 @@
         <v>38</v>
       </c>
       <c r="AW16" s="6" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AX16" s="9" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AY16" s="7"/>
     </row>
@@ -6408,7 +6408,7 @@
         <v>74</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M17" s="3" t="s">
         <v>75</v>
@@ -6426,13 +6426,13 @@
         <v>38</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T17" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="U17" s="4">
         <v>5</v>
@@ -6441,10 +6441,10 @@
         <v>204</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X17" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y17" s="3">
         <v>2</v>
@@ -6519,10 +6519,10 @@
         <v>38</v>
       </c>
       <c r="AW17" s="6" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AX17" s="9" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AY17" s="7"/>
     </row>
@@ -6561,7 +6561,7 @@
         <v>77</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="s">
@@ -6577,13 +6577,13 @@
         <v>38</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="U18" s="4">
         <v>5</v>
@@ -6592,10 +6592,10 @@
         <v>204</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X18" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y18" s="3">
         <v>3</v>
@@ -6670,10 +6670,10 @@
         <v>38</v>
       </c>
       <c r="AW18" s="6" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="AX18" s="9" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="AY18" s="7"/>
     </row>
@@ -6712,7 +6712,7 @@
         <v>78</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3" t="s">
@@ -6728,13 +6728,13 @@
         <v>38</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T19" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="U19" s="4">
         <v>5</v>
@@ -6743,10 +6743,10 @@
         <v>204</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X19" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y19" s="3">
         <v>7</v>
@@ -6821,10 +6821,10 @@
         <v>38</v>
       </c>
       <c r="AW19" s="6" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="AX19" s="9" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="AY19" s="7"/>
     </row>
@@ -6863,7 +6863,7 @@
         <v>78</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>75</v>
@@ -6881,13 +6881,13 @@
         <v>38</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T20" s="3" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="U20" s="4">
         <v>5</v>
@@ -6896,10 +6896,10 @@
         <v>204</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X20" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y20" s="3">
         <v>2</v>
@@ -6974,10 +6974,10 @@
         <v>38</v>
       </c>
       <c r="AW20" s="6" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="AX20" s="9" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="AY20" s="7"/>
     </row>
@@ -7016,7 +7016,7 @@
         <v>78</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3" t="s">
@@ -7032,13 +7032,13 @@
         <v>38</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T21" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="U21" s="4">
         <v>5</v>
@@ -7047,10 +7047,10 @@
         <v>204</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y21" s="3">
         <v>4</v>
@@ -7125,10 +7125,10 @@
         <v>38</v>
       </c>
       <c r="AW21" s="6" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="AX21" s="9" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="AY21" s="7"/>
     </row>
@@ -7167,7 +7167,7 @@
         <v>58</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3" t="s">
@@ -7183,13 +7183,13 @@
         <v>38</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T22" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="U22" s="4">
         <v>4</v>
@@ -7198,10 +7198,10 @@
         <v>204</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X22" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y22" s="3">
         <v>2</v>
@@ -7276,10 +7276,10 @@
         <v>38</v>
       </c>
       <c r="AW22" s="6" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="AX22" s="9" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AY22" s="7"/>
     </row>
@@ -7318,7 +7318,7 @@
         <v>80</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3" t="s">
@@ -7334,13 +7334,13 @@
         <v>38</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T23" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="U23" s="4">
         <v>5</v>
@@ -7349,10 +7349,10 @@
         <v>204</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X23" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y23" s="3">
         <v>2</v>
@@ -7391,7 +7391,7 @@
         <v>3</v>
       </c>
       <c r="AK23" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AL23" s="3" t="s">
         <v>42</v>
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="AS23" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AT23" s="3" t="s">
         <v>44</v>
@@ -7427,10 +7427,10 @@
         <v>38</v>
       </c>
       <c r="AW23" s="6" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="AX23" s="9" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="AY23" s="7"/>
     </row>
@@ -7469,7 +7469,7 @@
         <v>82</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3" t="s">
@@ -7485,13 +7485,13 @@
         <v>38</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="U24" s="4">
         <v>3</v>
@@ -7500,10 +7500,10 @@
         <v>204</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="X24" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y24" s="3">
         <v>3</v>
@@ -7578,10 +7578,10 @@
         <v>38</v>
       </c>
       <c r="AW24" s="6" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="AX24" s="9" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="AY24" s="7"/>
     </row>
@@ -7611,7 +7611,7 @@
         <v>35</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>36</v>
@@ -7620,7 +7620,7 @@
         <v>54</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3" t="s">
@@ -7636,13 +7636,13 @@
         <v>38</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T25" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="U25" s="4">
         <v>3</v>
@@ -7651,10 +7651,10 @@
         <v>204</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X25" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Y25" s="3">
         <v>3</v>
@@ -7729,10 +7729,10 @@
         <v>38</v>
       </c>
       <c r="AW25" s="6" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="AX25" s="9" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="AY25" s="7"/>
     </row>
@@ -7771,7 +7771,7 @@
         <v>54</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3" t="s">
@@ -7787,13 +7787,13 @@
         <v>38</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T26" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="U26" s="4">
         <v>3</v>
@@ -7802,10 +7802,10 @@
         <v>204</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X26" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y26" s="3">
         <v>5</v>
@@ -7880,10 +7880,10 @@
         <v>38</v>
       </c>
       <c r="AW26" s="6" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="AX26" s="9" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="AY26" s="7"/>
     </row>
@@ -7922,7 +7922,7 @@
         <v>58</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M27" s="3"/>
       <c r="N27" s="3" t="s">
@@ -7938,13 +7938,13 @@
         <v>38</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T27" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="U27" s="4">
         <v>4</v>
@@ -7953,10 +7953,10 @@
         <v>204</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X27" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y27" s="3">
         <v>4</v>
@@ -8031,10 +8031,10 @@
         <v>38</v>
       </c>
       <c r="AW27" s="6" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="AX27" s="9" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="AY27" s="7"/>
     </row>
@@ -8073,10 +8073,10 @@
         <v>58</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N28" s="3" t="s">
         <v>317</v>
@@ -8091,13 +8091,13 @@
         <v>36</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T28" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="U28" s="4">
         <v>4</v>
@@ -8106,10 +8106,10 @@
         <v>204</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X28" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y28" s="3">
         <v>2</v>
@@ -8184,10 +8184,10 @@
         <v>38</v>
       </c>
       <c r="AW28" s="6" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="AX28" s="9" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="AY28" s="7"/>
     </row>
@@ -8217,7 +8217,7 @@
         <v>35</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>36</v>
@@ -8226,7 +8226,7 @@
         <v>88</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M29" s="3"/>
       <c r="N29" s="3" t="s">
@@ -8242,13 +8242,13 @@
         <v>38</v>
       </c>
       <c r="R29" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T29" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="U29" s="4">
         <v>3</v>
@@ -8257,10 +8257,10 @@
         <v>204</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X29" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y29" s="3">
         <v>1</v>
@@ -8335,10 +8335,10 @@
         <v>38</v>
       </c>
       <c r="AW29" s="6" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="AX29" s="9" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="AY29" s="7"/>
     </row>
@@ -8368,7 +8368,7 @@
         <v>76</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>36</v>
@@ -8377,7 +8377,7 @@
         <v>37</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3" t="s">
@@ -8393,13 +8393,13 @@
         <v>38</v>
       </c>
       <c r="R30" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T30" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="U30" s="4">
         <v>3</v>
@@ -8408,10 +8408,10 @@
         <v>204</v>
       </c>
       <c r="W30" s="3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="X30" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y30" s="3">
         <v>3</v>
@@ -8486,10 +8486,10 @@
         <v>38</v>
       </c>
       <c r="AW30" s="6" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="AX30" s="9" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AY30" s="7"/>
     </row>
@@ -8528,7 +8528,7 @@
         <v>37</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M31" s="3"/>
       <c r="N31" s="3" t="s">
@@ -8544,13 +8544,13 @@
         <v>38</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T31" s="3" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="U31" s="4">
         <v>3</v>
@@ -8559,10 +8559,10 @@
         <v>204</v>
       </c>
       <c r="W31" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X31" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y31" s="3">
         <v>3</v>
@@ -8637,10 +8637,10 @@
         <v>38</v>
       </c>
       <c r="AW31" s="6" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="AX31" s="9" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="AY31" s="7"/>
     </row>
@@ -8679,7 +8679,7 @@
         <v>90</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="M32" s="3"/>
       <c r="N32" s="3" t="s">
@@ -8695,13 +8695,13 @@
         <v>38</v>
       </c>
       <c r="R32" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S32" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T32" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="U32" s="4">
         <v>3</v>
@@ -8710,10 +8710,10 @@
         <v>204</v>
       </c>
       <c r="W32" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X32" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y32" s="3">
         <v>1</v>
@@ -8788,10 +8788,10 @@
         <v>38</v>
       </c>
       <c r="AW32" s="6" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="AX32" s="9" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="AY32" s="7"/>
     </row>
@@ -8821,7 +8821,7 @@
         <v>35</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>36</v>
@@ -8830,7 +8830,7 @@
         <v>90</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="M33" s="3"/>
       <c r="N33" s="3" t="s">
@@ -8846,13 +8846,13 @@
         <v>38</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T33" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="U33" s="4">
         <v>3</v>
@@ -8861,10 +8861,10 @@
         <v>204</v>
       </c>
       <c r="W33" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X33" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y33" s="3">
         <v>2</v>
@@ -8939,10 +8939,10 @@
         <v>38</v>
       </c>
       <c r="AW33" s="6" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="AX33" s="9" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="AY33" s="7"/>
     </row>
@@ -8981,7 +8981,7 @@
         <v>298</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3" t="s">
@@ -8997,25 +8997,25 @@
         <v>38</v>
       </c>
       <c r="R34" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S34" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T34" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="U34" s="4">
         <v>3</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W34" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X34" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Y34" s="3">
         <v>1</v>
@@ -9090,10 +9090,10 @@
         <v>38</v>
       </c>
       <c r="AW34" s="6" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="AX34" s="9" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AY34" s="7"/>
     </row>
@@ -9132,7 +9132,7 @@
         <v>299</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="M35" s="3"/>
       <c r="N35" s="3" t="s">
@@ -9148,25 +9148,25 @@
         <v>38</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T35" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="U35" s="4">
         <v>3</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W35" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X35" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y35" s="3">
         <v>1</v>
@@ -9241,18 +9241,18 @@
         <v>38</v>
       </c>
       <c r="AW35" s="6" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="AX35" s="9" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="AY35" s="9" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="36" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>32</v>
@@ -9285,7 +9285,7 @@
         <v>300</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="M36" s="3"/>
       <c r="N36" s="3" t="s">
@@ -9301,25 +9301,25 @@
         <v>38</v>
       </c>
       <c r="R36" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="S36" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T36" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U36" s="4">
         <v>7</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W36" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X36" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Y36" s="3">
         <v>3</v>
@@ -9394,10 +9394,10 @@
         <v>38</v>
       </c>
       <c r="AW36" s="6" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="AX36" s="9" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="AY36" s="7"/>
     </row>
@@ -9436,7 +9436,7 @@
         <v>301</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="M37" s="3"/>
       <c r="N37" s="3" t="s">
@@ -9452,25 +9452,25 @@
         <v>38</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T37" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="U37" s="4">
         <v>3.5</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W37" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X37" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Y37" s="3">
         <v>3</v>
@@ -9545,16 +9545,16 @@
         <v>38</v>
       </c>
       <c r="AW37" s="6" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="AX37" s="9" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="AY37" s="7"/>
     </row>
     <row r="38" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="3" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>32</v>
@@ -9584,10 +9584,10 @@
         <v>36</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3" t="s">
@@ -9603,25 +9603,25 @@
         <v>38</v>
       </c>
       <c r="R38" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S38" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T38" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="U38" s="4">
         <v>3.5</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W38" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X38" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y38" s="3">
         <v>3</v>
@@ -9657,7 +9657,7 @@
         <v>41</v>
       </c>
       <c r="AJ38" s="3" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AK38" s="3" t="s">
         <v>36</v>
@@ -9681,7 +9681,7 @@
         <v>36</v>
       </c>
       <c r="AR38" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AS38" s="3" t="s">
         <v>36</v>
@@ -9696,13 +9696,13 @@
         <v>38</v>
       </c>
       <c r="AW38" s="6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="AX38" s="9" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="AY38" s="9" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="39" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -9740,7 +9740,7 @@
         <v>302</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3" t="s">
@@ -9756,25 +9756,25 @@
         <v>36</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T39" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="U39" s="4">
         <v>2</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W39" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X39" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y39" s="3">
         <v>2</v>
@@ -9849,16 +9849,16 @@
         <v>38</v>
       </c>
       <c r="AW39" s="6" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="AX39" s="9" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="AY39" s="7"/>
     </row>
     <row r="40" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>32</v>
@@ -9882,7 +9882,7 @@
         <v>35</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>36</v>
@@ -9891,7 +9891,7 @@
         <v>90</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3" t="s">
@@ -9907,25 +9907,25 @@
         <v>38</v>
       </c>
       <c r="R40" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S40" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T40" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="U40" s="4">
         <v>3</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W40" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X40" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y40" s="3">
         <v>2</v>
@@ -10000,16 +10000,16 @@
         <v>38</v>
       </c>
       <c r="AW40" s="6" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="AX40" s="9" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="AY40" s="7"/>
     </row>
     <row r="41" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>36</v>
@@ -10033,7 +10033,7 @@
         <v>35</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>36</v>
@@ -10042,7 +10042,7 @@
         <v>90</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3" t="s">
@@ -10058,13 +10058,13 @@
         <v>38</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T41" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="U41" s="4">
         <v>3</v>
@@ -10073,10 +10073,10 @@
         <v>204</v>
       </c>
       <c r="W41" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X41" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y41" s="3">
         <v>2</v>
@@ -10151,10 +10151,10 @@
         <v>38</v>
       </c>
       <c r="AW41" s="6" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="AX41" s="9" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AY41" s="7"/>
     </row>
@@ -10193,10 +10193,10 @@
         <v>105</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>313</v>
@@ -10211,13 +10211,13 @@
         <v>38</v>
       </c>
       <c r="R42" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S42" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T42" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="U42" s="4">
         <v>7</v>
@@ -10226,10 +10226,10 @@
         <v>204</v>
       </c>
       <c r="W42" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X42" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y42" s="3">
         <v>3</v>
@@ -10268,13 +10268,13 @@
         <v>16</v>
       </c>
       <c r="AK42" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AL42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM42" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AN42" s="3" t="s">
         <v>32</v>
@@ -10292,7 +10292,7 @@
         <v>5</v>
       </c>
       <c r="AS42" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AT42" s="3" t="s">
         <v>106</v>
@@ -10304,13 +10304,13 @@
         <v>38</v>
       </c>
       <c r="AW42" s="6" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="AX42" s="9" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AY42" s="9" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="43" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10348,10 +10348,10 @@
         <v>108</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="N43" s="3" t="s">
         <v>322</v>
@@ -10366,13 +10366,13 @@
         <v>38</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T43" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="U43" s="4">
         <v>8</v>
@@ -10381,10 +10381,10 @@
         <v>204</v>
       </c>
       <c r="W43" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X43" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y43" s="3">
         <v>3</v>
@@ -10423,13 +10423,13 @@
         <v>5</v>
       </c>
       <c r="AK43" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AL43" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM43" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AN43" s="3" t="s">
         <v>32</v>
@@ -10447,7 +10447,7 @@
         <v>3</v>
       </c>
       <c r="AS43" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AT43" s="3" t="s">
         <v>106</v>
@@ -10459,18 +10459,18 @@
         <v>38</v>
       </c>
       <c r="AW43" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AX43" s="9" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="AY43" s="9" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="44" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>32</v>
@@ -10500,10 +10500,10 @@
         <v>36</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="M44" s="3"/>
       <c r="N44" s="3" t="s">
@@ -10519,25 +10519,25 @@
         <v>38</v>
       </c>
       <c r="R44" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S44" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T44" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="U44" s="4">
         <v>5.5</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W44" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X44" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="Y44" s="3">
         <v>10</v>
@@ -10576,13 +10576,13 @@
         <v>6</v>
       </c>
       <c r="AK44" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AL44" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM44" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AN44" s="3" t="s">
         <v>83</v>
@@ -10612,18 +10612,18 @@
         <v>38</v>
       </c>
       <c r="AW44" s="6" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="AX44" s="9" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="AY44" s="9" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="45" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>32</v>
@@ -10656,7 +10656,7 @@
         <v>303</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="M45" s="3"/>
       <c r="N45" s="3" t="s">
@@ -10672,25 +10672,25 @@
         <v>38</v>
       </c>
       <c r="R45" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="S45" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T45" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="U45" s="4">
         <v>5</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W45" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X45" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Y45" s="3">
         <v>3</v>
@@ -10729,13 +10729,13 @@
         <v>3</v>
       </c>
       <c r="AK45" s="3" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AL45" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM45" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="AN45" s="3" t="s">
         <v>32</v>
@@ -10765,13 +10765,13 @@
         <v>38</v>
       </c>
       <c r="AW45" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AX45" s="7" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AY45" s="9" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="46" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -10809,7 +10809,7 @@
         <v>304</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="M46" s="3"/>
       <c r="N46" s="3" t="s">
@@ -10825,25 +10825,25 @@
         <v>38</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T46" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="U46" s="4">
         <v>7</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W46" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X46" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Y46" s="3">
         <v>4</v>
@@ -10882,7 +10882,7 @@
         <v>4</v>
       </c>
       <c r="AK46" s="3" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AL46" s="3" t="s">
         <v>46</v>
@@ -10918,7 +10918,7 @@
         <v>38</v>
       </c>
       <c r="AW46" s="6" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="AX46" s="7"/>
       <c r="AY46" s="7"/>
@@ -10955,13 +10955,13 @@
         <v>36</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>321</v>
@@ -10976,25 +10976,25 @@
         <v>38</v>
       </c>
       <c r="R47" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S47" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T47" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="U47" s="4">
         <v>10.5</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W47" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X47" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y47" s="3">
         <v>4</v>
@@ -11033,13 +11033,13 @@
         <v>10</v>
       </c>
       <c r="AK47" s="3" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AL47" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM47" s="3" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AN47" s="3" t="s">
         <v>32</v>
@@ -11069,13 +11069,13 @@
         <v>38</v>
       </c>
       <c r="AW47" s="6" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="AX47" s="9" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="AY47" s="9" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="48" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
@@ -11113,10 +11113,10 @@
         <v>118</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N48" s="3" t="s">
         <v>323</v>
@@ -11131,25 +11131,25 @@
         <v>38</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="T48" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="U48" s="4">
         <v>3.5</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W48" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="X48" s="3" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="Y48" s="3">
         <v>3</v>
@@ -11188,7 +11188,7 @@
         <v>15</v>
       </c>
       <c r="AK48" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AL48" s="3" t="s">
         <v>46</v>
@@ -11224,10 +11224,10 @@
         <v>38</v>
       </c>
       <c r="AW48" s="6" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="AX48" s="9" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AY48" s="7"/>
     </row>
@@ -11263,13 +11263,13 @@
         <v>36</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>319</v>
@@ -11284,25 +11284,25 @@
         <v>38</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T49" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="U49" s="4">
         <v>5</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W49" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X49" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y49" s="3">
         <v>3</v>
@@ -11341,13 +11341,13 @@
         <v>4</v>
       </c>
       <c r="AK49" s="3" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AL49" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM49" s="3" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AN49" s="3" t="s">
         <v>32</v>
@@ -11362,10 +11362,10 @@
         <v>36</v>
       </c>
       <c r="AR49" s="3" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AS49" s="3" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AT49" s="3" t="s">
         <v>44</v>
@@ -11377,18 +11377,18 @@
         <v>38</v>
       </c>
       <c r="AW49" s="6" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="AX49" s="9" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="AY49" s="9" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="50" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>32</v>
@@ -11418,10 +11418,10 @@
         <v>36</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3" t="s">
@@ -11437,25 +11437,25 @@
         <v>36</v>
       </c>
       <c r="R50" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S50" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T50" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="U50" s="4">
         <v>3.5</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W50" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X50" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="Y50" s="3">
         <v>3</v>
@@ -11530,16 +11530,16 @@
         <v>38</v>
       </c>
       <c r="AW50" s="6" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="AX50" s="9" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AY50" s="7"/>
     </row>
     <row r="51" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="3" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>32</v>
@@ -11572,7 +11572,7 @@
         <v>305</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3" t="s">
@@ -11588,25 +11588,25 @@
         <v>36</v>
       </c>
       <c r="R51" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S51" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T51" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="U51" s="4">
         <v>4</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W51" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X51" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y51" s="3">
         <v>1</v>
@@ -11645,13 +11645,13 @@
         <v>8</v>
       </c>
       <c r="AK51" s="3" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AL51" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM51" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AN51" s="3" t="s">
         <v>32</v>
@@ -11681,13 +11681,13 @@
         <v>38</v>
       </c>
       <c r="AW51" s="6" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="AX51" s="9" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="AY51" s="9" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="52" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -11725,7 +11725,7 @@
         <v>306</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3" t="s">
@@ -11741,25 +11741,25 @@
         <v>36</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T52" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U52" s="4">
         <v>7</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W52" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X52" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Y52" s="3">
         <v>7</v>
@@ -11798,13 +11798,13 @@
         <v>4</v>
       </c>
       <c r="AK52" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AL52" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM52" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AN52" s="3" t="s">
         <v>32</v>
@@ -11834,18 +11834,18 @@
         <v>38</v>
       </c>
       <c r="AW52" s="6" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="AX52" s="7" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="AY52" s="9" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="53" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>32</v>
@@ -11878,7 +11878,7 @@
         <v>123</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M53" s="3"/>
       <c r="N53" s="3" t="s">
@@ -11894,13 +11894,13 @@
         <v>38</v>
       </c>
       <c r="R53" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="S53" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T53" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="U53" s="4">
         <v>3</v>
@@ -11909,10 +11909,10 @@
         <v>204</v>
       </c>
       <c r="W53" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X53" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y53" s="3">
         <v>2</v>
@@ -11951,7 +11951,7 @@
         <v>6</v>
       </c>
       <c r="AK53" s="3" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AL53" s="3" t="s">
         <v>42</v>
@@ -11987,18 +11987,18 @@
         <v>38</v>
       </c>
       <c r="AW53" s="6" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="AX53" s="9" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="AY53" s="9" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="54" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>32</v>
@@ -12028,10 +12028,10 @@
         <v>36</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3" t="s">
@@ -12047,25 +12047,25 @@
         <v>36</v>
       </c>
       <c r="R54" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S54" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T54" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="U54" s="4">
         <v>3</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W54" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X54" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Y54" s="3">
         <v>7</v>
@@ -12140,16 +12140,16 @@
         <v>38</v>
       </c>
       <c r="AW54" s="6" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="AX54" s="9" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="AY54" s="7"/>
     </row>
     <row r="55" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="3" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>32</v>
@@ -12182,7 +12182,7 @@
         <v>307</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="M55" s="3"/>
       <c r="N55" s="3" t="s">
@@ -12198,25 +12198,25 @@
         <v>36</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T55" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="U55" s="4">
         <v>3</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W55" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X55" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y55" s="3">
         <v>3</v>
@@ -12291,10 +12291,10 @@
         <v>38</v>
       </c>
       <c r="AW55" s="6" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="AX55" s="9" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="AY55" s="7"/>
     </row>
@@ -12333,7 +12333,7 @@
         <v>307</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="M56" s="3"/>
       <c r="N56" s="3" t="s">
@@ -12349,25 +12349,25 @@
         <v>36</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T56" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="U56" s="4">
         <v>2.75</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W56" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X56" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="Y56" s="3">
         <v>3</v>
@@ -12442,10 +12442,10 @@
         <v>38</v>
       </c>
       <c r="AW56" s="6" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="AX56" s="9" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="AY56" s="7"/>
     </row>
@@ -12484,10 +12484,10 @@
         <v>308</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>319</v>
@@ -12502,25 +12502,25 @@
         <v>38</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T57" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="U57" s="4">
         <v>5</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W57" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X57" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y57" s="3">
         <v>2</v>
@@ -12556,16 +12556,16 @@
         <v>41</v>
       </c>
       <c r="AJ57" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AK57" s="3" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AL57" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM57" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="AN57" s="3" t="s">
         <v>83</v>
@@ -12580,7 +12580,7 @@
         <v>36</v>
       </c>
       <c r="AR57" s="3" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AS57" s="3" t="s">
         <v>36</v>
@@ -12595,18 +12595,18 @@
         <v>38</v>
       </c>
       <c r="AW57" s="6" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="AX57" s="9" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="AY57" s="9" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="58" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="3" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>32</v>
@@ -12639,13 +12639,13 @@
         <v>309</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N58" s="3" t="s">
-        <v>325</v>
+        <v>848</v>
       </c>
       <c r="O58" s="3">
         <v>1</v>
@@ -12657,25 +12657,25 @@
         <v>38</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T58" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="U58" s="4">
         <v>5.5</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W58" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X58" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Y58" s="3">
         <v>3</v>
@@ -12714,13 +12714,13 @@
         <v>4</v>
       </c>
       <c r="AK58" s="3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AL58" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM58" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AN58" s="3" t="s">
         <v>32</v>
@@ -12750,13 +12750,13 @@
         <v>38</v>
       </c>
       <c r="AW58" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="AX58" s="9" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AY58" s="9" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="59" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -12794,13 +12794,13 @@
         <v>309</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="N59" s="3" t="s">
-        <v>326</v>
+        <v>849</v>
       </c>
       <c r="O59" s="3">
         <v>4</v>
@@ -12812,13 +12812,13 @@
         <v>38</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T59" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="U59" s="4">
         <v>5</v>
@@ -12827,10 +12827,10 @@
         <v>204</v>
       </c>
       <c r="W59" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X59" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y59" s="3">
         <v>2</v>
@@ -12869,7 +12869,7 @@
         <v>4</v>
       </c>
       <c r="AK59" s="3" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AL59" s="3" t="s">
         <v>42</v>
@@ -12905,16 +12905,16 @@
         <v>38</v>
       </c>
       <c r="AW59" s="6" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="AX59" s="9" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="AY59" s="7"/>
     </row>
     <row r="60" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="3" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>36</v>
@@ -12947,10 +12947,10 @@
         <v>88</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="N60" s="3" t="s">
         <v>319</v>
@@ -12965,13 +12965,13 @@
         <v>38</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T60" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="U60" s="4">
         <v>5</v>
@@ -12980,10 +12980,10 @@
         <v>204</v>
       </c>
       <c r="W60" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X60" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y60" s="3">
         <v>3</v>
@@ -13022,13 +13022,13 @@
         <v>4</v>
       </c>
       <c r="AK60" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AL60" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM60" s="3" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AN60" s="3" t="s">
         <v>32</v>
@@ -13046,7 +13046,7 @@
         <v>6</v>
       </c>
       <c r="AS60" s="3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AT60" s="3" t="s">
         <v>106</v>
@@ -13058,18 +13058,18 @@
         <v>38</v>
       </c>
       <c r="AW60" s="6" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="AX60" s="7" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="AY60" s="9" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="61" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>32</v>
@@ -13084,7 +13084,7 @@
         <v>989804020</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>277</v>
@@ -13102,10 +13102,10 @@
         <v>310</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>319</v>
@@ -13120,25 +13120,25 @@
         <v>38</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T61" s="3" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="U61" s="4">
         <v>8</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W61" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X61" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y61" s="3">
         <v>4</v>
@@ -13177,13 +13177,13 @@
         <v>4</v>
       </c>
       <c r="AK61" s="3" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AL61" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM61" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AN61" s="3" t="s">
         <v>32</v>
@@ -13201,7 +13201,7 @@
         <v>4</v>
       </c>
       <c r="AS61" s="3" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AT61" s="3" t="s">
         <v>106</v>
@@ -13213,18 +13213,18 @@
         <v>38</v>
       </c>
       <c r="AW61" s="6" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="AX61" s="7" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="AY61" s="9" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="62" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>32</v>
@@ -13254,13 +13254,13 @@
         <v>36</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="N62" s="3" t="s">
         <v>319</v>
@@ -13275,25 +13275,25 @@
         <v>38</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T62" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="U62" s="4">
         <v>7</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W62" s="3" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X62" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Y62" s="3">
         <v>10</v>
@@ -13332,13 +13332,13 @@
         <v>15</v>
       </c>
       <c r="AK62" s="3" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AL62" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM62" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AN62" s="3" t="s">
         <v>32</v>
@@ -13350,7 +13350,7 @@
         <v>50</v>
       </c>
       <c r="AQ62" s="3" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AR62" s="3">
         <v>3</v>
@@ -13368,13 +13368,13 @@
         <v>38</v>
       </c>
       <c r="AW62" s="6" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AX62" s="9" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AY62" s="9" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="63" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -13409,13 +13409,13 @@
         <v>36</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="N63" s="3" t="s">
         <v>319</v>
@@ -13433,22 +13433,22 @@
         <v>98</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T63" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="U63" s="4">
         <v>7</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W63" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X63" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y63" s="3">
         <v>5</v>
@@ -13487,13 +13487,13 @@
         <v>5</v>
       </c>
       <c r="AK63" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AL63" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM63" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AN63" s="3" t="s">
         <v>32</v>
@@ -13502,7 +13502,7 @@
         <v>6</v>
       </c>
       <c r="AP63" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AQ63" s="3" t="s">
         <v>36</v>
@@ -13511,7 +13511,7 @@
         <v>26</v>
       </c>
       <c r="AS63" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AT63" s="3" t="s">
         <v>44</v>
@@ -13523,18 +13523,18 @@
         <v>38</v>
       </c>
       <c r="AW63" s="6" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="AX63" s="9" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="AY63" s="9" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="64" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>32</v>
@@ -13564,13 +13564,13 @@
         <v>36</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N64" s="3" t="s">
         <v>319</v>
@@ -13585,25 +13585,25 @@
         <v>38</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T64" s="3" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="U64" s="4">
         <v>5.5</v>
       </c>
       <c r="V64" s="3" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="W64" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X64" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Y64" s="3">
         <v>2</v>
@@ -13642,7 +13642,7 @@
         <v>6</v>
       </c>
       <c r="AK64" s="3" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AL64" s="3" t="s">
         <v>46</v>
@@ -13666,7 +13666,7 @@
         <v>1</v>
       </c>
       <c r="AS64" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AT64" s="3" t="s">
         <v>44</v>
@@ -13678,10 +13678,10 @@
         <v>38</v>
       </c>
       <c r="AW64" s="6" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="AX64" s="9" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="AY64" s="7"/>
     </row>
@@ -13717,10 +13717,10 @@
         <v>36</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="M65" s="3"/>
       <c r="N65" s="3" t="s">
@@ -13736,25 +13736,25 @@
         <v>38</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T65" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="U65" s="4">
         <v>3</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W65" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X65" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Y65" s="3">
         <v>1</v>
@@ -13793,13 +13793,13 @@
         <v>5</v>
       </c>
       <c r="AK65" s="3" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AL65" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM65" s="3" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AN65" s="3" t="s">
         <v>32</v>
@@ -13829,10 +13829,10 @@
         <v>38</v>
       </c>
       <c r="AW65" s="6" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="AX65" s="9" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="AY65" s="7"/>
     </row>
@@ -13868,10 +13868,10 @@
         <v>36</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3" t="s">
@@ -13887,25 +13887,25 @@
         <v>38</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T66" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="U66" s="4">
         <v>3</v>
       </c>
       <c r="V66" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W66" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X66" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y66" s="3">
         <v>2</v>
@@ -13944,7 +13944,7 @@
         <v>16</v>
       </c>
       <c r="AK66" s="3" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AL66" s="3" t="s">
         <v>46</v>
@@ -13980,10 +13980,10 @@
         <v>38</v>
       </c>
       <c r="AW66" s="6" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="AX66" s="9" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AY66" s="7"/>
     </row>
@@ -14004,7 +14004,7 @@
         <v>991322614</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>283</v>
@@ -14019,10 +14019,10 @@
         <v>36</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3" t="s">
@@ -14038,13 +14038,13 @@
         <v>38</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T67" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="U67" s="4">
         <v>3.5</v>
@@ -14053,10 +14053,10 @@
         <v>204</v>
       </c>
       <c r="W67" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X67" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Y67" s="3">
         <v>4</v>
@@ -14131,13 +14131,13 @@
         <v>38</v>
       </c>
       <c r="AW67" s="6" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="AX67" s="9" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="AY67" s="9" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="68" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14172,13 +14172,13 @@
         <v>36</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N68" s="3" t="s">
         <v>319</v>
@@ -14193,25 +14193,25 @@
         <v>38</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="T68" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="U68" s="4">
         <v>5</v>
       </c>
       <c r="V68" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W68" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X68" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y68" s="3">
         <v>5</v>
@@ -14250,13 +14250,13 @@
         <v>4</v>
       </c>
       <c r="AK68" s="3" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AL68" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM68" s="3" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AN68" s="3" t="s">
         <v>32</v>
@@ -14286,13 +14286,13 @@
         <v>38</v>
       </c>
       <c r="AW68" s="6" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="AX68" s="9" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="AY68" s="9" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="69" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14327,13 +14327,13 @@
         <v>36</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="N69" s="3" t="s">
         <v>319</v>
@@ -14348,25 +14348,25 @@
         <v>38</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T69" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="U69" s="4">
         <v>5</v>
       </c>
       <c r="V69" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W69" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X69" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y69" s="3">
         <v>3</v>
@@ -14405,13 +14405,13 @@
         <v>8</v>
       </c>
       <c r="AK69" s="3" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AL69" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM69" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AN69" s="3" t="s">
         <v>32</v>
@@ -14429,7 +14429,7 @@
         <v>3</v>
       </c>
       <c r="AS69" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AT69" s="3" t="s">
         <v>44</v>
@@ -14441,13 +14441,13 @@
         <v>38</v>
       </c>
       <c r="AW69" s="6" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="AX69" s="9" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="AY69" s="9" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="70" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14482,13 +14482,13 @@
         <v>36</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>319</v>
@@ -14503,25 +14503,25 @@
         <v>38</v>
       </c>
       <c r="R70" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S70" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T70" s="3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="U70" s="4">
         <v>12</v>
       </c>
       <c r="V70" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W70" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X70" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y70" s="3">
         <v>2</v>
@@ -14560,13 +14560,13 @@
         <v>12</v>
       </c>
       <c r="AK70" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AL70" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM70" s="3" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AN70" s="3" t="s">
         <v>32</v>
@@ -14596,13 +14596,13 @@
         <v>38</v>
       </c>
       <c r="AW70" s="6" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="AX70" s="9" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AY70" s="9" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="71" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14637,13 +14637,13 @@
         <v>36</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="N71" s="3" t="s">
         <v>319</v>
@@ -14658,25 +14658,25 @@
         <v>38</v>
       </c>
       <c r="R71" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="S71" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T71" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="U71" s="4">
         <v>10</v>
       </c>
       <c r="V71" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W71" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X71" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y71" s="3">
         <v>2</v>
@@ -14715,13 +14715,13 @@
         <v>12</v>
       </c>
       <c r="AK71" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AL71" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM71" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AN71" s="3" t="s">
         <v>32</v>
@@ -14739,7 +14739,7 @@
         <v>4</v>
       </c>
       <c r="AS71" s="3" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="AT71" s="3" t="s">
         <v>106</v>
@@ -14751,13 +14751,13 @@
         <v>38</v>
       </c>
       <c r="AW71" s="6" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="AX71" s="9" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AY71" s="9" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="72" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14792,10 +14792,10 @@
         <v>36</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="3" t="s">
@@ -14811,25 +14811,25 @@
         <v>38</v>
       </c>
       <c r="R72" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="S72" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T72" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="U72" s="4">
         <v>1</v>
       </c>
       <c r="V72" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="W72" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X72" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y72" s="3">
         <v>4</v>
@@ -14868,13 +14868,13 @@
         <v>20</v>
       </c>
       <c r="AK72" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AL72" s="3" t="s">
         <v>46</v>
       </c>
       <c r="AM72" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AN72" s="3" t="s">
         <v>32</v>
@@ -14904,13 +14904,13 @@
         <v>38</v>
       </c>
       <c r="AW72" s="6" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="AX72" s="9" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AY72" s="9" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="73" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
@@ -14945,10 +14945,10 @@
         <v>36</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M73" s="3"/>
       <c r="N73" s="3" t="s">
@@ -14964,25 +14964,25 @@
         <v>38</v>
       </c>
       <c r="R73" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S73" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T73" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="U73" s="4">
         <v>3</v>
       </c>
       <c r="V73" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W73" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X73" s="3" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y73" s="3">
         <v>2</v>
@@ -15027,7 +15027,7 @@
         <v>46</v>
       </c>
       <c r="AM73" s="3" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AN73" s="3" t="s">
         <v>32</v>
@@ -15057,10 +15057,10 @@
         <v>38</v>
       </c>
       <c r="AW73" s="6" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="AX73" s="9" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="AY73" s="7"/>
     </row>
@@ -15096,10 +15096,10 @@
         <v>36</v>
       </c>
       <c r="K74" s="3" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="3" t="s">
@@ -15115,25 +15115,25 @@
         <v>38</v>
       </c>
       <c r="R74" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S74" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T74" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="U74" s="4">
         <v>3.5</v>
       </c>
       <c r="V74" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W74" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X74" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Y74" s="3">
         <v>2</v>
@@ -15172,7 +15172,7 @@
         <v>10</v>
       </c>
       <c r="AK74" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AL74" s="3" t="s">
         <v>46</v>
@@ -15208,16 +15208,16 @@
         <v>38</v>
       </c>
       <c r="AW74" s="6" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="AX74" s="9" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AY74" s="7"/>
     </row>
     <row r="75" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>32</v>
@@ -15247,10 +15247,10 @@
         <v>36</v>
       </c>
       <c r="K75" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3" t="s">
@@ -15266,25 +15266,25 @@
         <v>38</v>
       </c>
       <c r="R75" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S75" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T75" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U75" s="4">
         <v>2.25</v>
       </c>
       <c r="V75" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="W75" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X75" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="Y75" s="3">
         <v>3</v>
@@ -15359,10 +15359,10 @@
         <v>38</v>
       </c>
       <c r="AW75" s="6" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="AX75" s="9" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AY75" s="7"/>
     </row>
@@ -15398,13 +15398,13 @@
         <v>36</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N76" s="3" t="s">
         <v>319</v>
@@ -15419,13 +15419,13 @@
         <v>38</v>
       </c>
       <c r="R76" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S76" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T76" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="U76" s="4">
         <v>3.5</v>
@@ -15434,10 +15434,10 @@
         <v>204</v>
       </c>
       <c r="W76" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X76" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y76" s="3">
         <v>3</v>
@@ -15476,13 +15476,13 @@
         <v>5</v>
       </c>
       <c r="AK76" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AL76" s="3" t="s">
         <v>42</v>
       </c>
       <c r="AM76" s="3" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AN76" s="3" t="s">
         <v>32</v>
@@ -15512,18 +15512,18 @@
         <v>38</v>
       </c>
       <c r="AW76" s="6" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="AX76" s="9" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="AY76" s="9" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="77" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="3" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>32</v>
@@ -15553,13 +15553,13 @@
         <v>36</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="L77" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="N77" s="3" t="s">
         <v>319</v>
@@ -15574,25 +15574,25 @@
         <v>38</v>
       </c>
       <c r="R77" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S77" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="T77" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="U77" s="4">
         <v>6</v>
       </c>
       <c r="V77" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W77" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X77" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="Y77" s="3">
         <v>2</v>
@@ -15631,7 +15631,7 @@
         <v>9</v>
       </c>
       <c r="AK77" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AL77" s="3" t="s">
         <v>42</v>
@@ -15655,7 +15655,7 @@
         <v>2</v>
       </c>
       <c r="AS77" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="AT77" s="3" t="s">
         <v>44</v>
@@ -15667,10 +15667,10 @@
         <v>38</v>
       </c>
       <c r="AW77" s="6" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="AX77" s="9" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="AY77" s="7"/>
     </row>
@@ -15706,10 +15706,10 @@
         <v>36</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="L78" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="3" t="s">
@@ -15725,25 +15725,25 @@
         <v>38</v>
       </c>
       <c r="R78" s="3" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="S78" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="T78" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="U78" s="4">
         <v>3.5</v>
       </c>
       <c r="V78" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="W78" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X78" s="3" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y78" s="3">
         <v>1</v>
@@ -15806,7 +15806,7 @@
         <v>1</v>
       </c>
       <c r="AS78" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="AT78" s="3" t="s">
         <v>44</v>
@@ -15818,18 +15818,18 @@
         <v>38</v>
       </c>
       <c r="AW78" s="6" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="AX78" s="9" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="AY78" s="9" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="79" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>32</v>
@@ -15859,10 +15859,10 @@
         <v>36</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3" t="s">
@@ -15878,13 +15878,13 @@
         <v>38</v>
       </c>
       <c r="R79" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S79" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T79" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="U79" s="4">
         <v>2.5</v>
@@ -15893,10 +15893,10 @@
         <v>204</v>
       </c>
       <c r="W79" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X79" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Y79" s="3">
         <v>1</v>
@@ -15971,16 +15971,16 @@
         <v>38</v>
       </c>
       <c r="AW79" s="6" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AX79" s="9" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AY79" s="7"/>
     </row>
     <row r="80" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>32</v>
@@ -16010,13 +16010,13 @@
         <v>36</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N80" s="3" t="s">
         <v>319</v>
@@ -16031,25 +16031,25 @@
         <v>38</v>
       </c>
       <c r="R80" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S80" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T80" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="U80" s="4">
         <v>6</v>
       </c>
       <c r="V80" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W80" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X80" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Y80" s="3">
         <v>2</v>
@@ -16124,18 +16124,18 @@
         <v>38</v>
       </c>
       <c r="AW80" s="6" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AX80" s="9" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AY80" s="9" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="81" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="3" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>32</v>
@@ -16168,10 +16168,10 @@
         <v>311</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>319</v>
@@ -16186,13 +16186,13 @@
         <v>38</v>
       </c>
       <c r="R81" s="3" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="S81" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T81" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="U81" s="4">
         <v>3</v>
@@ -16201,10 +16201,10 @@
         <v>204</v>
       </c>
       <c r="W81" s="3" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="X81" s="3" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Y81" s="3">
         <v>2</v>
@@ -16279,16 +16279,16 @@
         <v>38</v>
       </c>
       <c r="AW81" s="6" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="AX81" s="9" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="AY81" s="7"/>
     </row>
     <row r="82" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="12" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>32</v>
@@ -16318,13 +16318,13 @@
         <v>36</v>
       </c>
       <c r="K82" s="12" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="L82" s="12" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="M82" s="12" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="N82" s="12" t="s">
         <v>319</v>
@@ -16339,19 +16339,19 @@
         <v>38</v>
       </c>
       <c r="R82" s="12" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="T82" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="U82" s="13">
         <v>6</v>
       </c>
       <c r="V82" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="W82" s="14"/>
       <c r="X82" s="14"/>
@@ -16392,7 +16392,7 @@
         <v>10</v>
       </c>
       <c r="AK82" s="12" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AL82" s="12" t="s">
         <v>42</v>
@@ -16416,7 +16416,7 @@
         <v>1</v>
       </c>
       <c r="AS82" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="AT82" s="12" t="s">
         <v>106</v>
@@ -16428,18 +16428,18 @@
         <v>38</v>
       </c>
       <c r="AW82" s="16" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AX82" s="17" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AY82" s="9" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="83" spans="1:51" ht="20" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="3" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="B83" s="18" t="s">
         <v>32</v>
@@ -16448,16 +16448,16 @@
         <v>101</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E83" s="3">
         <v>917850039</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>35</v>
@@ -16469,14 +16469,14 @@
         <v>36</v>
       </c>
       <c r="K83" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="M83" s="19"/>
       <c r="N83" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="O83" s="19">
         <v>3</v>
@@ -16488,13 +16488,13 @@
         <v>38</v>
       </c>
       <c r="R83" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="S83" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="T83" s="3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="U83" s="20">
         <v>5</v>
@@ -16503,10 +16503,10 @@
         <v>204</v>
       </c>
       <c r="W83" s="3" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="X83" s="18" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="Y83" s="19">
         <v>2</v>
@@ -16533,7 +16533,7 @@
         <v>-79.287571</v>
       </c>
       <c r="AG83" s="18" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="AH83" s="19">
         <v>67</v>
@@ -16545,13 +16545,13 @@
         <v>12</v>
       </c>
       <c r="AK83" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="AL83" s="18" t="s">
         <v>46</v>
       </c>
       <c r="AM83" s="3" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="AN83" s="18" t="s">
         <v>38</v>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBB7FCA-32F5-CF46-96FF-8E5426EDF1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BCFFD5-3A5D-8E45-A093-65BA3001C30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28940" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3293" uniqueCount="875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3296" uniqueCount="878">
   <si>
     <t>nombre</t>
   </si>
@@ -2661,6 +2661,15 @@
   </si>
   <si>
     <t>Efectivo, Transferencia, App</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358351/MaryTierra_Vilcabamba02_inteext_web__wvtniq.jpg</t>
+  </si>
+  <si>
+    <t>{https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358343/MaryTierra_Vilcabamba02_idnt_web__hsjg1s.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358354/MaryTierra_Vilcabamba02_prdcntt_web__prn4zj.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358360/MaryTierra_Vilcabamba02_prddetailcen_web__pyhwpo.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358363/MaryTierra_Vilcabamba02_prddetailc_web__mxycfm.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358365/MaryTierra_Vilcabamba02_prddgn_web__x2vcrx.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358368/MaryTierra_Vilcabamba02_prddlpst_web__xkcdlo.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358371/MaryTierra_Vilcabamba02_prddtll_web__zdkc26.jpg, https://res.cloudinary.com/djl0e1p6e/image/upload/v1768358385/MaryTierra_Vilcabamba02_prdfrnt_web__afuftc.jpg}</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/djl0e1p6e/video/upload/v1780354427/MarYTierra_Vilcabamba_intro_low_horizontal_isv4dh.mp4</t>
   </si>
 </sst>
 </file>
@@ -17152,7 +17161,7 @@
         <v>35</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>420</v>
+        <v>54</v>
       </c>
       <c r="J85" s="17" t="s">
         <v>36</v>
@@ -17267,9 +17276,15 @@
       <c r="AV85" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="AW85" s="18"/>
-      <c r="AX85" s="18"/>
-      <c r="AY85" s="26"/>
+      <c r="AW85" s="17" t="s">
+        <v>876</v>
+      </c>
+      <c r="AX85" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="AY85" s="9" t="s">
+        <v>877</v>
+      </c>
       <c r="AZ85" s="20" t="s">
         <v>874</v>
       </c>
@@ -17394,6 +17409,8 @@
     <hyperlink ref="F59" r:id="rId115" xr:uid="{656A4746-F7E3-F540-9E90-A23B5ED1D8F4}"/>
     <hyperlink ref="F57" r:id="rId116" xr:uid="{23A15816-A188-5447-ADF2-2CDF9DA6C27B}"/>
     <hyperlink ref="F84" r:id="rId117" xr:uid="{48CC7A90-8A7E-E54B-A03E-75CC6A006517}"/>
+    <hyperlink ref="AX85" r:id="rId118" xr:uid="{CBEE1204-BABD-724A-8A01-155830775EF9}"/>
+    <hyperlink ref="AY85" r:id="rId119" xr:uid="{61523F3E-2990-6341-AD05-966C11B883D5}"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait"/>

--- a/media/csv_uploads/gastronomia_establecimiento1.xlsx
+++ b/media/csv_uploads/gastronomia_establecimiento1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/santigovinan/Documents/applications-django/emprendimientos/media/csv_uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BCFFD5-3A5D-8E45-A093-65BA3001C30B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032615FC-5AEE-7449-B598-D897B9F39F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28940" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17195,7 +17195,7 @@
         <v>818</v>
       </c>
       <c r="U85" s="21">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="V85" s="17" t="s">
         <v>819</v>
